--- a/research/traditional_assets/database/data/lithuania/lithuania_farming_agriculture.xlsx
+++ b/research/traditional_assets/database/data/lithuania/lithuania_farming_agriculture.xlsx
@@ -1400,7 +1400,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1537,22 +1537,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07794310438723719</v>
+        <v>0.07786443973065632</v>
       </c>
       <c r="C2">
-        <v>627.5424273012356</v>
+        <v>622.8268921167512</v>
       </c>
       <c r="D2">
-        <v>608.3424273012356</v>
+        <v>609.8348921167511</v>
       </c>
       <c r="E2">
-        <v>-420</v>
+        <v>-413.792</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>6.207999999999999</v>
       </c>
       <c r="G2">
         <v>19.2</v>
@@ -1573,28 +1573,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.3122623999999999</v>
       </c>
       <c r="N2">
-        <v>75.90000000000001</v>
+        <v>75.58773760000001</v>
       </c>
       <c r="O2">
-        <v>11.385</v>
+        <v>11.33816064</v>
       </c>
       <c r="P2">
-        <v>64.515</v>
+        <v>64.24957696000001</v>
       </c>
       <c r="Q2">
-        <v>82.11500000000001</v>
+        <v>81.84957696000001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07794310438723719</v>
+        <v>0.07821908053601649</v>
       </c>
       <c r="T2">
-        <v>0.5887122450442503</v>
+        <v>0.5937668451279635</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>243.0648070340842</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1619,22 +1619,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07786443973065632</v>
+        <v>0.07778577507407547</v>
       </c>
       <c r="C3">
-        <v>622.8268921167512</v>
+        <v>618.1186979600764</v>
       </c>
       <c r="D3">
-        <v>609.8348921167511</v>
+        <v>611.3346979600764</v>
       </c>
       <c r="E3">
-        <v>-413.792</v>
+        <v>-407.584</v>
       </c>
       <c r="F3">
-        <v>6.207999999999999</v>
+        <v>12.416</v>
       </c>
       <c r="G3">
         <v>19.2</v>
@@ -1655,28 +1655,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M3">
-        <v>0.3122623999999999</v>
+        <v>0.6245247999999999</v>
       </c>
       <c r="N3">
-        <v>75.58773760000001</v>
+        <v>75.2754752</v>
       </c>
       <c r="O3">
-        <v>11.33816064</v>
+        <v>11.29132128</v>
       </c>
       <c r="P3">
-        <v>64.24957696000001</v>
+        <v>63.98415392</v>
       </c>
       <c r="Q3">
-        <v>81.84957696000001</v>
+        <v>81.58415392000001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07821908053601649</v>
+        <v>0.07850068885109743</v>
       </c>
       <c r="T3">
-        <v>0.5937668451279635</v>
+        <v>0.5989246003154262</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>243.0648070340842</v>
+        <v>121.5324035170421</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1701,22 +1701,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07778577507407547</v>
+        <v>0.0777071104174946</v>
       </c>
       <c r="C4">
-        <v>618.1186979600764</v>
+        <v>613.4178991275198</v>
       </c>
       <c r="D4">
-        <v>611.3346979600764</v>
+        <v>612.8418991275198</v>
       </c>
       <c r="E4">
-        <v>-407.584</v>
+        <v>-401.376</v>
       </c>
       <c r="F4">
-        <v>12.416</v>
+        <v>18.624</v>
       </c>
       <c r="G4">
         <v>19.2</v>
@@ -1737,28 +1737,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M4">
-        <v>0.6245247999999999</v>
+        <v>0.9367871999999999</v>
       </c>
       <c r="N4">
-        <v>75.2754752</v>
+        <v>74.96321280000001</v>
       </c>
       <c r="O4">
-        <v>11.29132128</v>
+        <v>11.24448192</v>
       </c>
       <c r="P4">
-        <v>63.98415392</v>
+        <v>63.71873088000001</v>
       </c>
       <c r="Q4">
-        <v>81.58415392000001</v>
+        <v>81.31873088</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07850068885109743</v>
+        <v>0.07878810352319032</v>
       </c>
       <c r="T4">
-        <v>0.5989246003154262</v>
+        <v>0.6041887009706713</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>121.5324035170421</v>
+        <v>81.02160234469473</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1783,22 +1783,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0777071104174946</v>
+        <v>0.07762844576091377</v>
       </c>
       <c r="C5">
-        <v>613.4178991275198</v>
+        <v>608.7245504521666</v>
       </c>
       <c r="D5">
-        <v>612.8418991275198</v>
+        <v>614.3565504521665</v>
       </c>
       <c r="E5">
-        <v>-401.376</v>
+        <v>-395.168</v>
       </c>
       <c r="F5">
-        <v>18.624</v>
+        <v>24.832</v>
       </c>
       <c r="G5">
         <v>19.2</v>
@@ -1819,28 +1819,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M5">
-        <v>0.9367871999999999</v>
+        <v>1.2490496</v>
       </c>
       <c r="N5">
-        <v>74.96321280000001</v>
+        <v>74.6509504</v>
       </c>
       <c r="O5">
-        <v>11.24448192</v>
+        <v>11.19764256</v>
       </c>
       <c r="P5">
-        <v>63.71873088000001</v>
+        <v>63.45330784</v>
       </c>
       <c r="Q5">
-        <v>81.31873088</v>
+        <v>81.05330784</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07878810352319032</v>
+        <v>0.07908150600095185</v>
       </c>
       <c r="T5">
-        <v>0.6041887009706713</v>
+        <v>0.6095624703895676</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>81.02160234469473</v>
+        <v>60.76620175852105</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1865,22 +1865,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07762844576091377</v>
+        <v>0.0775497811043329</v>
       </c>
       <c r="C6">
-        <v>608.7245504521666</v>
+        <v>604.0387073105309</v>
       </c>
       <c r="D6">
-        <v>614.3565504521665</v>
+        <v>615.8787073105308</v>
       </c>
       <c r="E6">
-        <v>-395.168</v>
+        <v>-388.96</v>
       </c>
       <c r="F6">
-        <v>24.832</v>
+        <v>31.04</v>
       </c>
       <c r="G6">
         <v>19.2</v>
@@ -1901,28 +1901,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M6">
-        <v>1.2490496</v>
+        <v>1.561312</v>
       </c>
       <c r="N6">
-        <v>74.6509504</v>
+        <v>74.338688</v>
       </c>
       <c r="O6">
-        <v>11.19764256</v>
+        <v>11.1508032</v>
       </c>
       <c r="P6">
-        <v>63.45330784</v>
+        <v>63.18788480000001</v>
       </c>
       <c r="Q6">
-        <v>81.05330784</v>
+        <v>80.7878848</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07908150600095185</v>
+        <v>0.07938108537298201</v>
       </c>
       <c r="T6">
-        <v>0.6095624703895676</v>
+        <v>0.61504937179623</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>60.76620175852105</v>
+        <v>48.61296140681684</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1947,22 +1947,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0775497811043329</v>
+        <v>0.07747111644775205</v>
       </c>
       <c r="C7">
-        <v>604.0387073105309</v>
+        <v>599.3604256293014</v>
       </c>
       <c r="D7">
-        <v>615.8787073105308</v>
+        <v>617.4084256293014</v>
       </c>
       <c r="E7">
-        <v>-388.96</v>
+        <v>-382.752</v>
       </c>
       <c r="F7">
-        <v>31.04</v>
+        <v>37.248</v>
       </c>
       <c r="G7">
         <v>19.2</v>
@@ -1983,28 +1983,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M7">
-        <v>1.561312</v>
+        <v>1.8735744</v>
       </c>
       <c r="N7">
-        <v>74.338688</v>
+        <v>74.02642560000001</v>
       </c>
       <c r="O7">
-        <v>11.1508032</v>
+        <v>11.10396384</v>
       </c>
       <c r="P7">
-        <v>63.18788480000001</v>
+        <v>62.92246176000001</v>
       </c>
       <c r="Q7">
-        <v>80.7878848</v>
+        <v>80.52246176000001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07938108537298201</v>
+        <v>0.07968703877420431</v>
       </c>
       <c r="T7">
-        <v>0.61504937179623</v>
+        <v>0.6206530157860128</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>48.61296140681684</v>
+        <v>40.51080117234737</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07747111644775204</v>
+        <v>0.0773924517911712</v>
       </c>
       <c r="C8">
-        <v>599.3604256293016</v>
+        <v>594.6897618921939</v>
       </c>
       <c r="D8">
-        <v>617.4084256293016</v>
+        <v>618.9457618921939</v>
       </c>
       <c r="E8">
-        <v>-382.752</v>
+        <v>-376.544</v>
       </c>
       <c r="F8">
-        <v>37.248</v>
+        <v>43.45599999999999</v>
       </c>
       <c r="G8">
         <v>19.2</v>
@@ -2065,28 +2065,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M8">
-        <v>1.8735744</v>
+        <v>2.185836799999999</v>
       </c>
       <c r="N8">
-        <v>74.02642560000001</v>
+        <v>73.7141632</v>
       </c>
       <c r="O8">
-        <v>11.10396384</v>
+        <v>11.05712448</v>
       </c>
       <c r="P8">
-        <v>62.92246176000001</v>
+        <v>62.65703872</v>
       </c>
       <c r="Q8">
-        <v>80.52246176000001</v>
+        <v>80.25703872</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07968703877420431</v>
+        <v>0.07999957181846365</v>
       </c>
       <c r="T8">
-        <v>0.6206530157860128</v>
+        <v>0.6263771682486943</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>40.51080117234737</v>
+        <v>34.72354386201204</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2111,22 +2111,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0773924517911712</v>
+        <v>0.07731378713459035</v>
       </c>
       <c r="C9">
-        <v>594.6897618921939</v>
+        <v>590.0267731469022</v>
       </c>
       <c r="D9">
-        <v>618.9457618921939</v>
+        <v>620.4907731469021</v>
       </c>
       <c r="E9">
-        <v>-376.544</v>
+        <v>-370.336</v>
       </c>
       <c r="F9">
-        <v>43.456</v>
+        <v>49.66399999999999</v>
       </c>
       <c r="G9">
         <v>19.2</v>
@@ -2147,28 +2147,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M9">
-        <v>2.1858368</v>
+        <v>2.4980992</v>
       </c>
       <c r="N9">
-        <v>73.7141632</v>
+        <v>73.40190080000001</v>
       </c>
       <c r="O9">
-        <v>11.05712448</v>
+        <v>11.01028512</v>
       </c>
       <c r="P9">
-        <v>62.65703872</v>
+        <v>62.39161568000001</v>
       </c>
       <c r="Q9">
-        <v>80.25703872</v>
+        <v>79.99161568000001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07999957181846365</v>
+        <v>0.08031889905933733</v>
       </c>
       <c r="T9">
-        <v>0.6263771682486943</v>
+        <v>0.6322257588083906</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>34.72354386201202</v>
+        <v>30.38310087926053</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2193,22 +2193,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07731378713459035</v>
+        <v>0.0772351224780095</v>
       </c>
       <c r="C10">
-        <v>590.0267731469022</v>
+        <v>585.3715170121546</v>
       </c>
       <c r="D10">
-        <v>620.4907731469021</v>
+        <v>622.0435170121546</v>
       </c>
       <c r="E10">
-        <v>-370.336</v>
+        <v>-364.128</v>
       </c>
       <c r="F10">
-        <v>49.66399999999999</v>
+        <v>55.87199999999999</v>
       </c>
       <c r="G10">
         <v>19.2</v>
@@ -2229,28 +2229,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M10">
-        <v>2.4980992</v>
+        <v>2.810361599999999</v>
       </c>
       <c r="N10">
-        <v>73.40190080000001</v>
+        <v>73.08963840000001</v>
       </c>
       <c r="O10">
-        <v>11.01028512</v>
+        <v>10.96344576</v>
       </c>
       <c r="P10">
-        <v>62.39161568000001</v>
+        <v>62.12619264000001</v>
       </c>
       <c r="Q10">
-        <v>79.99161568000001</v>
+        <v>79.72619264000002</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08031889905933733</v>
+        <v>0.08064524448132911</v>
       </c>
       <c r="T10">
-        <v>0.6322257588083906</v>
+        <v>0.6382028898199483</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>30.38310087926053</v>
+        <v>27.00720078156492</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2275,22 +2275,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0772351224780095</v>
+        <v>0.07715645782142863</v>
       </c>
       <c r="C11">
-        <v>585.3715170121546</v>
+        <v>580.7240516848776</v>
       </c>
       <c r="D11">
-        <v>622.0435170121546</v>
+        <v>623.6040516848776</v>
       </c>
       <c r="E11">
-        <v>-364.128</v>
+        <v>-357.92</v>
       </c>
       <c r="F11">
-        <v>55.87199999999999</v>
+        <v>62.07999999999999</v>
       </c>
       <c r="G11">
         <v>19.2</v>
@@ -2311,28 +2311,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M11">
-        <v>2.810361599999999</v>
+        <v>3.122624</v>
       </c>
       <c r="N11">
-        <v>73.08963840000001</v>
+        <v>72.777376</v>
       </c>
       <c r="O11">
-        <v>10.96344576</v>
+        <v>10.9166064</v>
       </c>
       <c r="P11">
-        <v>62.12619264000001</v>
+        <v>61.8607696</v>
       </c>
       <c r="Q11">
-        <v>79.72619264000002</v>
+        <v>79.46076960000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08064524448132911</v>
+        <v>0.08097884202380959</v>
       </c>
       <c r="T11">
-        <v>0.6382028898199483</v>
+        <v>0.6443128459650963</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2349,7 +2349,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>27.00720078156492</v>
+        <v>24.30648070340842</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2357,22 +2357,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07715645782142863</v>
+        <v>0.07707779316484778</v>
       </c>
       <c r="C12">
-        <v>580.7240516848776</v>
+        <v>576.0844359474653</v>
       </c>
       <c r="D12">
-        <v>623.6040516848776</v>
+        <v>625.1724359474653</v>
       </c>
       <c r="E12">
-        <v>-357.92</v>
+        <v>-351.712</v>
       </c>
       <c r="F12">
-        <v>62.08</v>
+        <v>68.288</v>
       </c>
       <c r="G12">
         <v>19.2</v>
@@ -2393,28 +2393,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M12">
-        <v>3.122624</v>
+        <v>3.434886399999999</v>
       </c>
       <c r="N12">
-        <v>72.777376</v>
+        <v>72.46511360000001</v>
       </c>
       <c r="O12">
-        <v>10.9166064</v>
+        <v>10.86976704</v>
       </c>
       <c r="P12">
-        <v>61.8607696</v>
+        <v>61.59534656000001</v>
       </c>
       <c r="Q12">
-        <v>79.46076960000001</v>
+        <v>79.19534656000002</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08097884202380959</v>
+        <v>0.08131993614027841</v>
       </c>
       <c r="T12">
-        <v>0.6443128459650963</v>
+        <v>0.6505601044955284</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>24.30648070340842</v>
+        <v>22.0968006394622</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2439,22 +2439,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07707779316484778</v>
+        <v>0.07699912850826693</v>
       </c>
       <c r="C13">
-        <v>576.0844359474653</v>
+        <v>571.4527291751621</v>
       </c>
       <c r="D13">
-        <v>625.1724359474653</v>
+        <v>626.748729175162</v>
       </c>
       <c r="E13">
-        <v>-351.712</v>
+        <v>-345.504</v>
       </c>
       <c r="F13">
-        <v>68.288</v>
+        <v>74.496</v>
       </c>
       <c r="G13">
         <v>19.2</v>
@@ -2475,28 +2475,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M13">
-        <v>3.434886399999999</v>
+        <v>3.7471488</v>
       </c>
       <c r="N13">
-        <v>72.46511360000001</v>
+        <v>72.1528512</v>
       </c>
       <c r="O13">
-        <v>10.86976704</v>
+        <v>10.82292768</v>
       </c>
       <c r="P13">
-        <v>61.59534656000001</v>
+        <v>61.32992352</v>
       </c>
       <c r="Q13">
-        <v>79.19534656000002</v>
+        <v>78.92992352</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08131993614027841</v>
+        <v>0.08166878239575787</v>
       </c>
       <c r="T13">
-        <v>0.6505601044955284</v>
+        <v>0.6569493461743794</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>22.0968006394622</v>
+        <v>20.25540058617368</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2521,22 +2521,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07699912850826693</v>
+        <v>0.07692046385168606</v>
       </c>
       <c r="C14">
-        <v>571.4527291751621</v>
+        <v>566.8289913435547</v>
       </c>
       <c r="D14">
-        <v>626.748729175162</v>
+        <v>628.3329913435546</v>
       </c>
       <c r="E14">
-        <v>-345.504</v>
+        <v>-339.296</v>
       </c>
       <c r="F14">
-        <v>74.496</v>
+        <v>80.70399999999999</v>
       </c>
       <c r="G14">
         <v>19.2</v>
@@ -2557,28 +2557,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M14">
-        <v>3.7471488</v>
+        <v>4.0594112</v>
       </c>
       <c r="N14">
-        <v>72.1528512</v>
+        <v>71.84058880000001</v>
       </c>
       <c r="O14">
-        <v>10.82292768</v>
+        <v>10.77608832</v>
       </c>
       <c r="P14">
-        <v>61.32992352</v>
+        <v>61.06450048000001</v>
       </c>
       <c r="Q14">
-        <v>78.92992352</v>
+        <v>78.66450048000002</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08166878239575787</v>
+        <v>0.08202564810538628</v>
       </c>
       <c r="T14">
-        <v>0.6569493461743794</v>
+        <v>0.6634854669722844</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>20.25540058617368</v>
+        <v>18.69729284877571</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2603,22 +2603,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07692046385168606</v>
+        <v>0.07684179919510518</v>
       </c>
       <c r="C15">
-        <v>566.8289913435547</v>
+        <v>562.213283036179</v>
       </c>
       <c r="D15">
-        <v>628.3329913435546</v>
+        <v>629.9252830361789</v>
       </c>
       <c r="E15">
-        <v>-339.296</v>
+        <v>-333.088</v>
       </c>
       <c r="F15">
-        <v>80.70399999999999</v>
+        <v>86.91200000000001</v>
       </c>
       <c r="G15">
         <v>19.2</v>
@@ -2639,28 +2639,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M15">
-        <v>4.0594112</v>
+        <v>4.3716736</v>
       </c>
       <c r="N15">
-        <v>71.84058880000001</v>
+        <v>71.52832640000001</v>
       </c>
       <c r="O15">
-        <v>10.77608832</v>
+        <v>10.72924896</v>
       </c>
       <c r="P15">
-        <v>61.06450048000001</v>
+        <v>60.79907744000001</v>
       </c>
       <c r="Q15">
-        <v>78.66450048000002</v>
+        <v>78.39907744000001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08202564810538628</v>
+        <v>0.08239081301756418</v>
       </c>
       <c r="T15">
-        <v>0.6634854669722844</v>
+        <v>0.670173590579443</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2677,7 +2677,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>18.69729284877571</v>
+        <v>17.36177193100601</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2685,22 +2685,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07684179919510518</v>
+        <v>0.07676313453852435</v>
       </c>
       <c r="C16">
-        <v>562.213283036179</v>
+        <v>557.6056654522413</v>
       </c>
       <c r="D16">
-        <v>629.9252830361789</v>
+        <v>631.5256654522412</v>
       </c>
       <c r="E16">
-        <v>-333.088</v>
+        <v>-326.88</v>
       </c>
       <c r="F16">
-        <v>86.91200000000001</v>
+        <v>93.12</v>
       </c>
       <c r="G16">
         <v>19.2</v>
@@ -2721,28 +2721,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M16">
-        <v>4.3716736</v>
+        <v>4.683936</v>
       </c>
       <c r="N16">
-        <v>71.52832640000001</v>
+        <v>71.216064</v>
       </c>
       <c r="O16">
-        <v>10.72924896</v>
+        <v>10.6824096</v>
       </c>
       <c r="P16">
-        <v>60.79907744000001</v>
+        <v>60.5336544</v>
       </c>
       <c r="Q16">
-        <v>78.39907744000001</v>
+        <v>78.13365440000001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08239081301756418</v>
+        <v>0.08276457004532277</v>
       </c>
       <c r="T16">
-        <v>0.670173590579443</v>
+        <v>0.6770190818008879</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>17.36177193100601</v>
+        <v>16.20432046893895</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2767,22 +2767,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07676313453852435</v>
+        <v>0.0766844698819435</v>
       </c>
       <c r="C17">
-        <v>557.6056654522413</v>
+        <v>553.0062004144633</v>
       </c>
       <c r="D17">
-        <v>631.5256654522412</v>
+        <v>633.1342004144632</v>
       </c>
       <c r="E17">
-        <v>-326.88</v>
+        <v>-320.672</v>
       </c>
       <c r="F17">
-        <v>93.11999999999999</v>
+        <v>99.32799999999999</v>
       </c>
       <c r="G17">
         <v>19.2</v>
@@ -2803,28 +2803,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M17">
-        <v>4.683935999999999</v>
+        <v>4.996198399999999</v>
       </c>
       <c r="N17">
-        <v>71.216064</v>
+        <v>70.90380160000001</v>
       </c>
       <c r="O17">
-        <v>10.6824096</v>
+        <v>10.63557024</v>
       </c>
       <c r="P17">
-        <v>60.5336544</v>
+        <v>60.26823136000001</v>
       </c>
       <c r="Q17">
-        <v>78.13365440000001</v>
+        <v>77.86823136000001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08276457004532277</v>
+        <v>0.08314722604993274</v>
       </c>
       <c r="T17">
-        <v>0.6770190818008879</v>
+        <v>0.6840275609085577</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>16.20432046893895</v>
+        <v>15.19155043963026</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2849,22 +2849,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0766844698819435</v>
+        <v>0.07660580522536262</v>
       </c>
       <c r="C18">
-        <v>553.0062004144633</v>
+        <v>548.4149503770386</v>
       </c>
       <c r="D18">
-        <v>633.1342004144632</v>
+        <v>634.7509503770386</v>
       </c>
       <c r="E18">
-        <v>-320.672</v>
+        <v>-314.464</v>
       </c>
       <c r="F18">
-        <v>99.32799999999999</v>
+        <v>105.536</v>
       </c>
       <c r="G18">
         <v>19.2</v>
@@ -2885,28 +2885,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M18">
-        <v>4.996198399999999</v>
+        <v>5.3084608</v>
       </c>
       <c r="N18">
-        <v>70.90380160000001</v>
+        <v>70.5915392</v>
       </c>
       <c r="O18">
-        <v>10.63557024</v>
+        <v>10.58873088</v>
       </c>
       <c r="P18">
-        <v>60.26823136000001</v>
+        <v>60.00280832</v>
       </c>
       <c r="Q18">
-        <v>77.86823136000001</v>
+        <v>77.60280832000001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08314722604993274</v>
+        <v>0.0835391026811598</v>
       </c>
       <c r="T18">
-        <v>0.6840275609085577</v>
+        <v>0.6912049190308698</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>15.19155043963026</v>
+        <v>14.29792982553436</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2931,22 +2931,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07660580522536262</v>
+        <v>0.07652714056878179</v>
       </c>
       <c r="C19">
-        <v>548.4149503770386</v>
+        <v>543.8319784337168</v>
       </c>
       <c r="D19">
-        <v>634.7509503770386</v>
+        <v>636.3759784337168</v>
       </c>
       <c r="E19">
-        <v>-314.464</v>
+        <v>-308.256</v>
       </c>
       <c r="F19">
-        <v>105.536</v>
+        <v>111.744</v>
       </c>
       <c r="G19">
         <v>19.2</v>
@@ -2967,28 +2967,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M19">
-        <v>5.3084608</v>
+        <v>5.6207232</v>
       </c>
       <c r="N19">
-        <v>70.5915392</v>
+        <v>70.27927680000001</v>
       </c>
       <c r="O19">
-        <v>10.58873088</v>
+        <v>10.54189152</v>
       </c>
       <c r="P19">
-        <v>60.00280832</v>
+        <v>59.73738528000001</v>
       </c>
       <c r="Q19">
-        <v>77.60280832000001</v>
+        <v>77.33738528000001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.0835391026811598</v>
+        <v>0.08394053727900218</v>
       </c>
       <c r="T19">
-        <v>0.6912049190308698</v>
+        <v>0.6985573346683605</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>14.29792982553436</v>
+        <v>13.50360039078246</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3013,22 +3013,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07652714056878179</v>
+        <v>0.07669072591220093</v>
       </c>
       <c r="C20">
-        <v>543.8319784337168</v>
+        <v>534.2539772472231</v>
       </c>
       <c r="D20">
-        <v>636.3759784337168</v>
+        <v>633.0059772472231</v>
       </c>
       <c r="E20">
-        <v>-308.256</v>
+        <v>-302.048</v>
       </c>
       <c r="F20">
-        <v>111.744</v>
+        <v>117.952</v>
       </c>
       <c r="G20">
         <v>19.2</v>
@@ -3049,45 +3049,45 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M20">
-        <v>5.620723199999999</v>
+        <v>6.1099136</v>
       </c>
       <c r="N20">
-        <v>70.27927680000001</v>
+        <v>69.79008640000001</v>
       </c>
       <c r="O20">
-        <v>10.54189152</v>
+        <v>10.46851296</v>
       </c>
       <c r="P20">
-        <v>59.73738528000001</v>
+        <v>59.32157344000001</v>
       </c>
       <c r="Q20">
-        <v>77.33738528000001</v>
+        <v>76.92157344</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08394053727900218</v>
+        <v>0.08435188384222336</v>
       </c>
       <c r="T20">
-        <v>0.6985573346683605</v>
+        <v>0.7060912914327027</v>
       </c>
       <c r="U20">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V20">
         <v>0.15</v>
       </c>
       <c r="W20">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y20">
-        <v>13.50360039078246</v>
+        <v>12.42243425504413</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07669072591220093</v>
+        <v>0.07662481125562007</v>
       </c>
       <c r="C21">
-        <v>534.2539772472231</v>
+        <v>529.3995742330368</v>
       </c>
       <c r="D21">
-        <v>633.0059772472231</v>
+        <v>634.3595742330367</v>
       </c>
       <c r="E21">
-        <v>-302.048</v>
+        <v>-295.84</v>
       </c>
       <c r="F21">
-        <v>117.952</v>
+        <v>124.16</v>
       </c>
       <c r="G21">
         <v>19.2</v>
@@ -3131,28 +3131,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M21">
-        <v>6.1099136</v>
+        <v>6.431488</v>
       </c>
       <c r="N21">
-        <v>69.79008640000001</v>
+        <v>69.468512</v>
       </c>
       <c r="O21">
-        <v>10.46851296</v>
+        <v>10.4202768</v>
       </c>
       <c r="P21">
-        <v>59.32157344000001</v>
+        <v>59.04823520000001</v>
       </c>
       <c r="Q21">
-        <v>76.92157344</v>
+        <v>76.64823520000002</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08435188384222336</v>
+        <v>0.08477351406952509</v>
       </c>
       <c r="T21">
-        <v>0.7060912914327027</v>
+        <v>0.7138135971161534</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3169,7 +3169,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>12.42243425504413</v>
+        <v>11.80131254229192</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3177,22 +3177,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07662481125562007</v>
+        <v>0.07655889659903922</v>
       </c>
       <c r="C22">
-        <v>529.3995742330368</v>
+        <v>524.550972589532</v>
       </c>
       <c r="D22">
-        <v>634.3595742330367</v>
+        <v>635.718972589532</v>
       </c>
       <c r="E22">
-        <v>-295.84</v>
+        <v>-289.632</v>
       </c>
       <c r="F22">
-        <v>124.16</v>
+        <v>130.368</v>
       </c>
       <c r="G22">
         <v>19.2</v>
@@ -3213,28 +3213,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M22">
-        <v>6.431488</v>
+        <v>6.753062399999999</v>
       </c>
       <c r="N22">
-        <v>69.468512</v>
+        <v>69.1469376</v>
       </c>
       <c r="O22">
-        <v>10.4202768</v>
+        <v>10.37204064</v>
       </c>
       <c r="P22">
-        <v>59.04823520000001</v>
+        <v>58.77489696</v>
       </c>
       <c r="Q22">
-        <v>76.64823520000002</v>
+        <v>76.37489696</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08477351406952509</v>
+        <v>0.08520581847979648</v>
       </c>
       <c r="T22">
-        <v>0.7138135971161534</v>
+        <v>0.721731404209312</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.80131254229192</v>
+        <v>11.23934527837326</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3259,22 +3259,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07655889659903921</v>
+        <v>0.07649298194245838</v>
       </c>
       <c r="C23">
-        <v>524.5509725895324</v>
+        <v>519.7082096928779</v>
       </c>
       <c r="D23">
-        <v>635.7189725895323</v>
+        <v>637.0842096928778</v>
       </c>
       <c r="E23">
-        <v>-289.632</v>
+        <v>-283.424</v>
       </c>
       <c r="F23">
-        <v>130.368</v>
+        <v>136.576</v>
       </c>
       <c r="G23">
         <v>19.2</v>
@@ -3295,28 +3295,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M23">
-        <v>6.753062399999999</v>
+        <v>7.0746368</v>
       </c>
       <c r="N23">
-        <v>69.1469376</v>
+        <v>68.82536320000001</v>
       </c>
       <c r="O23">
-        <v>10.37204064</v>
+        <v>10.32380448</v>
       </c>
       <c r="P23">
-        <v>58.77489696</v>
+        <v>58.50155872000001</v>
       </c>
       <c r="Q23">
-        <v>76.37489696</v>
+        <v>76.10155872000001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08520581847979647</v>
+        <v>0.08564920761853637</v>
       </c>
       <c r="T23">
-        <v>0.7217314042093119</v>
+        <v>0.7298522319971668</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.23934527837326</v>
+        <v>10.72846594753812</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3341,22 +3341,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07649298194245838</v>
+        <v>0.0764270672858775</v>
       </c>
       <c r="C24">
-        <v>519.7082096928779</v>
+        <v>514.8713232410028</v>
       </c>
       <c r="D24">
-        <v>637.0842096928778</v>
+        <v>638.4553232410027</v>
       </c>
       <c r="E24">
-        <v>-283.424</v>
+        <v>-277.216</v>
       </c>
       <c r="F24">
-        <v>136.576</v>
+        <v>142.784</v>
       </c>
       <c r="G24">
         <v>19.2</v>
@@ -3377,28 +3377,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M24">
-        <v>7.0746368</v>
+        <v>7.3962112</v>
       </c>
       <c r="N24">
-        <v>68.82536320000001</v>
+        <v>68.50378880000001</v>
       </c>
       <c r="O24">
-        <v>10.32380448</v>
+        <v>10.27556832</v>
       </c>
       <c r="P24">
-        <v>58.50155872000001</v>
+        <v>58.22822048</v>
       </c>
       <c r="Q24">
-        <v>76.10155872000001</v>
+        <v>75.82822048</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08564920761853637</v>
+        <v>0.08610411335828247</v>
       </c>
       <c r="T24">
-        <v>0.7298522319971668</v>
+        <v>0.7381839903769138</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.72846594753812</v>
+        <v>10.26201090634081</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3423,22 +3423,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0764270672858775</v>
+        <v>0.07636115262929664</v>
       </c>
       <c r="C25">
-        <v>514.8713232410028</v>
+        <v>510.0403512570638</v>
       </c>
       <c r="D25">
-        <v>638.4553232410027</v>
+        <v>639.8323512570637</v>
       </c>
       <c r="E25">
-        <v>-277.216</v>
+        <v>-271.008</v>
       </c>
       <c r="F25">
-        <v>142.784</v>
+        <v>148.992</v>
       </c>
       <c r="G25">
         <v>19.2</v>
@@ -3459,28 +3459,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M25">
-        <v>7.3962112</v>
+        <v>7.717785599999999</v>
       </c>
       <c r="N25">
-        <v>68.50378880000001</v>
+        <v>68.18221440000001</v>
       </c>
       <c r="O25">
-        <v>10.27556832</v>
+        <v>10.22733216</v>
       </c>
       <c r="P25">
-        <v>58.22822048</v>
+        <v>57.95488224</v>
       </c>
       <c r="Q25">
-        <v>75.82822048</v>
+        <v>75.55488224000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08610411335828247</v>
+        <v>0.08657099030170612</v>
       </c>
       <c r="T25">
-        <v>0.7381839903769138</v>
+        <v>0.746735005556128</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>10.26201090634081</v>
+        <v>9.834427118576604</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3505,22 +3505,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07636115262929664</v>
+        <v>0.07665648797271579</v>
       </c>
       <c r="C26">
-        <v>510.0403512570638</v>
+        <v>497.7083520723128</v>
       </c>
       <c r="D26">
-        <v>639.8323512570637</v>
+        <v>633.7083520723128</v>
       </c>
       <c r="E26">
-        <v>-271.008</v>
+        <v>-264.8</v>
       </c>
       <c r="F26">
-        <v>148.992</v>
+        <v>155.2</v>
       </c>
       <c r="G26">
         <v>19.2</v>
@@ -3541,45 +3541,45 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M26">
-        <v>7.717785599999999</v>
+        <v>8.303199999999999</v>
       </c>
       <c r="N26">
-        <v>68.18221440000001</v>
+        <v>67.5968</v>
       </c>
       <c r="O26">
-        <v>10.22733216</v>
+        <v>10.13952</v>
       </c>
       <c r="P26">
-        <v>57.95488224</v>
+        <v>57.45728</v>
       </c>
       <c r="Q26">
-        <v>75.55488224000001</v>
+        <v>75.05728000000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08657099030170612</v>
+        <v>0.08705031729695439</v>
       </c>
       <c r="T26">
-        <v>0.746735005556128</v>
+        <v>0.7555140478067879</v>
       </c>
       <c r="U26">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V26">
         <v>0.15</v>
       </c>
       <c r="W26">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>9.834427118576604</v>
+        <v>9.141054051450045</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3587,22 +3587,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07665648797271579</v>
+        <v>0.07660502331613495</v>
       </c>
       <c r="C27">
-        <v>497.7083520723128</v>
+        <v>492.5590619579416</v>
       </c>
       <c r="D27">
-        <v>633.7083520723128</v>
+        <v>634.7670619579416</v>
       </c>
       <c r="E27">
-        <v>-264.8</v>
+        <v>-258.592</v>
       </c>
       <c r="F27">
-        <v>155.2</v>
+        <v>161.408</v>
       </c>
       <c r="G27">
         <v>19.2</v>
@@ -3623,28 +3623,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M27">
-        <v>8.303199999999999</v>
+        <v>8.635327999999999</v>
       </c>
       <c r="N27">
-        <v>67.5968</v>
+        <v>67.264672</v>
       </c>
       <c r="O27">
-        <v>10.13952</v>
+        <v>10.0897008</v>
       </c>
       <c r="P27">
-        <v>57.45728</v>
+        <v>57.1749712</v>
       </c>
       <c r="Q27">
-        <v>75.05728000000001</v>
+        <v>74.77497120000001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08705031729695439</v>
+        <v>0.08754259907585803</v>
       </c>
       <c r="T27">
-        <v>0.7555140478067879</v>
+        <v>0.7645303614696278</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3661,7 +3661,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>9.141054051450045</v>
+        <v>8.789475049471196</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3669,22 +3669,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07660502331613495</v>
+        <v>0.07655355865955409</v>
       </c>
       <c r="C28">
-        <v>492.5590619579416</v>
+        <v>487.4133152475249</v>
       </c>
       <c r="D28">
-        <v>634.7670619579416</v>
+        <v>635.8293152475248</v>
       </c>
       <c r="E28">
-        <v>-258.592</v>
+        <v>-252.384</v>
       </c>
       <c r="F28">
-        <v>161.408</v>
+        <v>167.616</v>
       </c>
       <c r="G28">
         <v>19.2</v>
@@ -3705,28 +3705,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M28">
-        <v>8.635327999999999</v>
+        <v>8.967455999999999</v>
       </c>
       <c r="N28">
-        <v>67.264672</v>
+        <v>66.93254400000001</v>
       </c>
       <c r="O28">
-        <v>10.0897008</v>
+        <v>10.0398816</v>
       </c>
       <c r="P28">
-        <v>57.1749712</v>
+        <v>56.89266240000001</v>
       </c>
       <c r="Q28">
-        <v>74.77497120000001</v>
+        <v>74.4926624</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08754259907585803</v>
+        <v>0.08804836802678642</v>
       </c>
       <c r="T28">
-        <v>0.7645303614696278</v>
+        <v>0.7737936974246004</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.789475049471196</v>
+        <v>8.463938936527821</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3751,22 +3751,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07655355865955409</v>
+        <v>0.07650209400297323</v>
       </c>
       <c r="C29">
-        <v>487.4133152475249</v>
+        <v>482.2711297600493</v>
       </c>
       <c r="D29">
-        <v>635.8293152475248</v>
+        <v>636.8951297600493</v>
       </c>
       <c r="E29">
-        <v>-252.384</v>
+        <v>-246.176</v>
       </c>
       <c r="F29">
-        <v>167.616</v>
+        <v>173.824</v>
       </c>
       <c r="G29">
         <v>19.2</v>
@@ -3787,28 +3787,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M29">
-        <v>8.967455999999999</v>
+        <v>9.299584000000001</v>
       </c>
       <c r="N29">
-        <v>66.93254400000001</v>
+        <v>66.60041600000001</v>
       </c>
       <c r="O29">
-        <v>10.0398816</v>
+        <v>9.990062400000001</v>
       </c>
       <c r="P29">
-        <v>56.89266240000001</v>
+        <v>56.61035360000001</v>
       </c>
       <c r="Q29">
-        <v>74.4926624</v>
+        <v>74.21035360000002</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08804836802678642</v>
+        <v>0.0885681861152406</v>
       </c>
       <c r="T29">
-        <v>0.7737936974246004</v>
+        <v>0.783314348267211</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3825,7 +3825,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.463938936527821</v>
+        <v>8.161655403080395</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3833,22 +3833,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07650209400297323</v>
+        <v>0.07645062934639237</v>
       </c>
       <c r="C30">
-        <v>482.2711297600493</v>
+        <v>477.1325234341789</v>
       </c>
       <c r="D30">
-        <v>636.8951297600493</v>
+        <v>637.9645234341789</v>
       </c>
       <c r="E30">
-        <v>-246.176</v>
+        <v>-239.968</v>
       </c>
       <c r="F30">
-        <v>173.824</v>
+        <v>180.032</v>
       </c>
       <c r="G30">
         <v>19.2</v>
@@ -3869,28 +3869,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M30">
-        <v>9.299584000000001</v>
+        <v>9.631712</v>
       </c>
       <c r="N30">
-        <v>66.60041600000001</v>
+        <v>66.26828800000001</v>
       </c>
       <c r="O30">
-        <v>9.990062400000001</v>
+        <v>9.940243200000001</v>
       </c>
       <c r="P30">
-        <v>56.61035360000001</v>
+        <v>56.32804480000001</v>
       </c>
       <c r="Q30">
-        <v>74.21035360000002</v>
+        <v>73.92804480000001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.0885681861152406</v>
+        <v>0.08910264696674983</v>
       </c>
       <c r="T30">
-        <v>0.783314348267211</v>
+        <v>0.7931031864575007</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.161655403080395</v>
+        <v>7.880219009870729</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3915,22 +3915,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07645062934639237</v>
+        <v>0.07639916468981152</v>
       </c>
       <c r="C31">
-        <v>477.1325234341789</v>
+        <v>471.9975143292617</v>
       </c>
       <c r="D31">
-        <v>637.9645234341789</v>
+        <v>639.0375143292616</v>
       </c>
       <c r="E31">
-        <v>-239.968</v>
+        <v>-233.76</v>
       </c>
       <c r="F31">
-        <v>180.032</v>
+        <v>186.24</v>
       </c>
       <c r="G31">
         <v>19.2</v>
@@ -3951,28 +3951,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M31">
-        <v>9.631711999999998</v>
+        <v>9.963839999999999</v>
       </c>
       <c r="N31">
-        <v>66.26828800000001</v>
+        <v>65.93616</v>
       </c>
       <c r="O31">
-        <v>9.940243200000001</v>
+        <v>9.890423999999999</v>
       </c>
       <c r="P31">
-        <v>56.32804480000001</v>
+        <v>56.04573600000001</v>
       </c>
       <c r="Q31">
-        <v>73.92804480000001</v>
+        <v>73.645736</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08910264696674983</v>
+        <v>0.08965237812830217</v>
       </c>
       <c r="T31">
-        <v>0.7931031864575007</v>
+        <v>0.8031717057389416</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.880219009870729</v>
+        <v>7.617545042875037</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3997,22 +3997,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07639916468981152</v>
+        <v>0.07655850003323066</v>
       </c>
       <c r="C32">
-        <v>471.9975143292617</v>
+        <v>462.4791688412384</v>
       </c>
       <c r="D32">
-        <v>639.0375143292616</v>
+        <v>635.7271688412384</v>
       </c>
       <c r="E32">
-        <v>-233.76</v>
+        <v>-227.552</v>
       </c>
       <c r="F32">
-        <v>186.24</v>
+        <v>192.448</v>
       </c>
       <c r="G32">
         <v>19.2</v>
@@ -4033,45 +4033,45 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M32">
-        <v>9.963839999999999</v>
+        <v>10.4499264</v>
       </c>
       <c r="N32">
-        <v>65.93616</v>
+        <v>65.45007360000001</v>
       </c>
       <c r="O32">
-        <v>9.890423999999999</v>
+        <v>9.817511040000001</v>
       </c>
       <c r="P32">
-        <v>56.04573600000001</v>
+        <v>55.63256256000001</v>
       </c>
       <c r="Q32">
-        <v>73.645736</v>
+        <v>73.23256256000002</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08965237812830217</v>
+        <v>0.09021804352642125</v>
       </c>
       <c r="T32">
-        <v>0.8031717057389416</v>
+        <v>0.813532066158975</v>
       </c>
       <c r="U32">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V32">
         <v>0.15</v>
       </c>
       <c r="W32">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y32">
-        <v>7.617545042875037</v>
+        <v>7.263209049969961</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4079,22 +4079,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07655850003323066</v>
+        <v>0.0765138353766498</v>
       </c>
       <c r="C33">
-        <v>462.4791688412384</v>
+        <v>457.1956556507565</v>
       </c>
       <c r="D33">
-        <v>635.7271688412384</v>
+        <v>636.6516556507564</v>
       </c>
       <c r="E33">
-        <v>-227.552</v>
+        <v>-221.344</v>
       </c>
       <c r="F33">
-        <v>192.448</v>
+        <v>198.656</v>
       </c>
       <c r="G33">
         <v>19.2</v>
@@ -4115,28 +4115,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M33">
-        <v>10.4499264</v>
+        <v>10.7870208</v>
       </c>
       <c r="N33">
-        <v>65.45007360000001</v>
+        <v>65.11297920000001</v>
       </c>
       <c r="O33">
-        <v>9.817511040000001</v>
+        <v>9.766946880000001</v>
       </c>
       <c r="P33">
-        <v>55.63256256000001</v>
+        <v>55.34603232000001</v>
       </c>
       <c r="Q33">
-        <v>73.23256256000002</v>
+        <v>72.94603232000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09021804352642125</v>
+        <v>0.09080034614213206</v>
       </c>
       <c r="T33">
-        <v>0.813532066158975</v>
+        <v>0.8241971430619505</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.263209049969961</v>
+        <v>7.0362337671584</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0765138353766498</v>
+        <v>0.07646917072006895</v>
       </c>
       <c r="C34">
-        <v>457.1956556507565</v>
+        <v>451.91483518948</v>
       </c>
       <c r="D34">
-        <v>636.6516556507564</v>
+        <v>637.5788351894799</v>
       </c>
       <c r="E34">
-        <v>-221.344</v>
+        <v>-215.136</v>
       </c>
       <c r="F34">
-        <v>198.656</v>
+        <v>204.864</v>
       </c>
       <c r="G34">
         <v>19.2</v>
@@ -4197,28 +4197,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M34">
-        <v>10.7870208</v>
+        <v>11.1241152</v>
       </c>
       <c r="N34">
-        <v>65.11297920000001</v>
+        <v>64.7758848</v>
       </c>
       <c r="O34">
-        <v>9.766946880000001</v>
+        <v>9.71638272</v>
       </c>
       <c r="P34">
-        <v>55.34603232000001</v>
+        <v>55.05950208</v>
       </c>
       <c r="Q34">
-        <v>72.94603232000001</v>
+        <v>72.65950208000001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09080034614213206</v>
+        <v>0.09140003092547605</v>
       </c>
       <c r="T34">
-        <v>0.8241971430619505</v>
+        <v>0.8351805804694925</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.0362337671584</v>
+        <v>6.823014562092992</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4243,22 +4243,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07646917072006895</v>
+        <v>0.07642450606348808</v>
       </c>
       <c r="C35">
-        <v>451.91483518948</v>
+        <v>446.6367192391339</v>
       </c>
       <c r="D35">
-        <v>637.5788351894799</v>
+        <v>638.5087192391338</v>
       </c>
       <c r="E35">
-        <v>-215.136</v>
+        <v>-208.928</v>
       </c>
       <c r="F35">
-        <v>204.864</v>
+        <v>211.072</v>
       </c>
       <c r="G35">
         <v>19.2</v>
@@ -4279,28 +4279,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M35">
-        <v>11.1241152</v>
+        <v>11.4612096</v>
       </c>
       <c r="N35">
-        <v>64.7758848</v>
+        <v>64.4387904</v>
       </c>
       <c r="O35">
-        <v>9.71638272</v>
+        <v>9.66581856</v>
       </c>
       <c r="P35">
-        <v>55.05950208</v>
+        <v>54.77297184</v>
       </c>
       <c r="Q35">
-        <v>72.65950208000001</v>
+        <v>72.37297184000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09140003092547605</v>
+        <v>0.09201788797498195</v>
       </c>
       <c r="T35">
-        <v>0.8351805804694925</v>
+        <v>0.8464968493136267</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4317,7 +4317,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.823014562092992</v>
+        <v>6.622337663207905</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4325,22 +4325,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07642450606348808</v>
+        <v>0.07637984140690723</v>
       </c>
       <c r="C36">
-        <v>446.6367192391339</v>
+        <v>441.3613196502745</v>
       </c>
       <c r="D36">
-        <v>638.5087192391338</v>
+        <v>639.4413196502744</v>
       </c>
       <c r="E36">
-        <v>-208.928</v>
+        <v>-202.72</v>
       </c>
       <c r="F36">
-        <v>211.072</v>
+        <v>217.28</v>
       </c>
       <c r="G36">
         <v>19.2</v>
@@ -4361,28 +4361,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M36">
-        <v>11.4612096</v>
+        <v>11.798304</v>
       </c>
       <c r="N36">
-        <v>64.4387904</v>
+        <v>64.101696</v>
       </c>
       <c r="O36">
-        <v>9.66581856</v>
+        <v>9.6152544</v>
       </c>
       <c r="P36">
-        <v>54.77297184</v>
+        <v>54.48644160000001</v>
       </c>
       <c r="Q36">
-        <v>72.37297184000001</v>
+        <v>72.0864416</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09201788797498195</v>
+        <v>0.09265475601062652</v>
       </c>
       <c r="T36">
-        <v>0.8464968493136267</v>
+        <v>0.8581613110452727</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.622337663207905</v>
+        <v>6.433128015687679</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4407,22 +4407,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07637984140690723</v>
+        <v>0.07633517675032638</v>
       </c>
       <c r="C37">
-        <v>441.3613196502745</v>
+        <v>436.0886483427958</v>
       </c>
       <c r="D37">
-        <v>639.4413196502744</v>
+        <v>640.3766483427958</v>
       </c>
       <c r="E37">
-        <v>-202.72</v>
+        <v>-196.512</v>
       </c>
       <c r="F37">
-        <v>217.28</v>
+        <v>223.488</v>
       </c>
       <c r="G37">
         <v>19.2</v>
@@ -4443,28 +4443,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M37">
-        <v>11.798304</v>
+        <v>12.1353984</v>
       </c>
       <c r="N37">
-        <v>64.101696</v>
+        <v>63.76460160000001</v>
       </c>
       <c r="O37">
-        <v>9.6152544</v>
+        <v>9.564690240000001</v>
       </c>
       <c r="P37">
-        <v>54.48644160000001</v>
+        <v>54.19991136</v>
       </c>
       <c r="Q37">
-        <v>72.0864416</v>
+        <v>71.79991136000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09265475601062652</v>
+        <v>0.09331152617238497</v>
       </c>
       <c r="T37">
-        <v>0.8581613110452727</v>
+        <v>0.8701902872060326</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.433128015687679</v>
+        <v>6.25443001525191</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4489,22 +4489,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07633517675032639</v>
+        <v>0.07660501209374553</v>
       </c>
       <c r="C38">
-        <v>436.0886483427955</v>
+        <v>424.2712932061274</v>
       </c>
       <c r="D38">
-        <v>640.3766483427954</v>
+        <v>634.7672932061273</v>
       </c>
       <c r="E38">
-        <v>-196.512</v>
+        <v>-190.304</v>
       </c>
       <c r="F38">
-        <v>223.488</v>
+        <v>229.696</v>
       </c>
       <c r="G38">
         <v>19.2</v>
@@ -4525,45 +4525,45 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M38">
-        <v>12.1353984</v>
+        <v>12.7021888</v>
       </c>
       <c r="N38">
-        <v>63.76460160000001</v>
+        <v>63.1978112</v>
       </c>
       <c r="O38">
-        <v>9.564690240000001</v>
+        <v>9.479671680000001</v>
       </c>
       <c r="P38">
-        <v>54.19991136</v>
+        <v>53.71813952</v>
       </c>
       <c r="Q38">
-        <v>71.79991136000001</v>
+        <v>71.31813952</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09331152617238497</v>
+        <v>0.09398914618054845</v>
       </c>
       <c r="T38">
-        <v>0.8701902872060325</v>
+        <v>0.8826011356258642</v>
       </c>
       <c r="U38">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V38">
         <v>0.15</v>
       </c>
       <c r="W38">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y38">
-        <v>6.254430015251911</v>
+        <v>5.975348122679456</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4571,22 +4571,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07660501209374553</v>
+        <v>0.07656884743716466</v>
       </c>
       <c r="C39">
-        <v>424.2712932061274</v>
+        <v>418.8093770890042</v>
       </c>
       <c r="D39">
-        <v>634.7672932061273</v>
+        <v>635.5133770890042</v>
       </c>
       <c r="E39">
-        <v>-190.304</v>
+        <v>-184.096</v>
       </c>
       <c r="F39">
-        <v>229.696</v>
+        <v>235.904</v>
       </c>
       <c r="G39">
         <v>19.2</v>
@@ -4607,28 +4607,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M39">
-        <v>12.7021888</v>
+        <v>13.0454912</v>
       </c>
       <c r="N39">
-        <v>63.1978112</v>
+        <v>62.8545088</v>
       </c>
       <c r="O39">
-        <v>9.479671680000001</v>
+        <v>9.42817632</v>
       </c>
       <c r="P39">
-        <v>53.71813952</v>
+        <v>53.42633248000001</v>
       </c>
       <c r="Q39">
-        <v>71.31813952</v>
+        <v>71.02633248000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09398914618054845</v>
+        <v>0.09468862489865269</v>
       </c>
       <c r="T39">
-        <v>0.8826011356258642</v>
+        <v>0.8954123339947228</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.975348122679456</v>
+        <v>5.818102119451049</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4653,22 +4653,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07656884743716466</v>
+        <v>0.07653268278058381</v>
       </c>
       <c r="C40">
-        <v>418.8093770890042</v>
+        <v>413.3492168789453</v>
       </c>
       <c r="D40">
-        <v>635.5133770890042</v>
+        <v>636.2612168789452</v>
       </c>
       <c r="E40">
-        <v>-184.096</v>
+        <v>-177.888</v>
       </c>
       <c r="F40">
-        <v>235.904</v>
+        <v>242.112</v>
       </c>
       <c r="G40">
         <v>19.2</v>
@@ -4689,28 +4689,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M40">
-        <v>13.0454912</v>
+        <v>13.3887936</v>
       </c>
       <c r="N40">
-        <v>62.8545088</v>
+        <v>62.51120640000001</v>
       </c>
       <c r="O40">
-        <v>9.42817632</v>
+        <v>9.37668096</v>
       </c>
       <c r="P40">
-        <v>53.42633248000001</v>
+        <v>53.13452544</v>
       </c>
       <c r="Q40">
-        <v>71.02633248000001</v>
+        <v>70.73452544</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09468862489865269</v>
+        <v>0.09541103734521936</v>
       </c>
       <c r="T40">
-        <v>0.8954123339947228</v>
+        <v>0.9086435716543634</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4727,7 +4727,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.818102119451049</v>
+        <v>5.668920013824099</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4735,22 +4735,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07653268278058381</v>
+        <v>0.07649651812400296</v>
       </c>
       <c r="C41">
-        <v>413.3492168789453</v>
+        <v>407.8908187820403</v>
       </c>
       <c r="D41">
-        <v>636.2612168789452</v>
+        <v>637.0108187820402</v>
       </c>
       <c r="E41">
-        <v>-177.888</v>
+        <v>-171.68</v>
       </c>
       <c r="F41">
-        <v>242.112</v>
+        <v>248.32</v>
       </c>
       <c r="G41">
         <v>19.2</v>
@@ -4771,28 +4771,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M41">
-        <v>13.3887936</v>
+        <v>13.732096</v>
       </c>
       <c r="N41">
-        <v>62.51120640000001</v>
+        <v>62.16790400000001</v>
       </c>
       <c r="O41">
-        <v>9.37668096</v>
+        <v>9.325185600000001</v>
       </c>
       <c r="P41">
-        <v>53.13452544</v>
+        <v>52.84271840000001</v>
       </c>
       <c r="Q41">
-        <v>70.73452544</v>
+        <v>70.44271840000002</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09541103734521936</v>
+        <v>0.0961575302066716</v>
       </c>
       <c r="T41">
-        <v>0.9086435716543634</v>
+        <v>0.9223158505693256</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4809,7 +4809,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.668920013824099</v>
+        <v>5.527197013478497</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4817,22 +4817,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07649651812400296</v>
+        <v>0.0764603534674221</v>
       </c>
       <c r="C42">
-        <v>407.8908187820403</v>
+        <v>402.4341890336593</v>
       </c>
       <c r="D42">
-        <v>637.0108187820402</v>
+        <v>637.7621890336593</v>
       </c>
       <c r="E42">
-        <v>-171.68</v>
+        <v>-165.472</v>
       </c>
       <c r="F42">
-        <v>248.32</v>
+        <v>254.528</v>
       </c>
       <c r="G42">
         <v>19.2</v>
@@ -4853,28 +4853,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M42">
-        <v>13.732096</v>
+        <v>14.0753984</v>
       </c>
       <c r="N42">
-        <v>62.16790400000001</v>
+        <v>61.82460160000001</v>
       </c>
       <c r="O42">
-        <v>9.325185600000001</v>
+        <v>9.273690240000001</v>
       </c>
       <c r="P42">
-        <v>52.84271840000001</v>
+        <v>52.55091136000001</v>
       </c>
       <c r="Q42">
-        <v>70.44271840000002</v>
+        <v>70.15091136000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.0961575302066716</v>
+        <v>0.09692932791088492</v>
       </c>
       <c r="T42">
-        <v>0.9223158505693256</v>
+        <v>0.9364515965661508</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4891,7 +4891,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.527197013478497</v>
+        <v>5.392387330222924</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4899,22 +4899,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0764603534674221</v>
+        <v>0.07642418881084125</v>
       </c>
       <c r="C43">
-        <v>402.4341890336593</v>
+        <v>396.9793338986261</v>
       </c>
       <c r="D43">
-        <v>637.7621890336593</v>
+        <v>638.5153338986261</v>
       </c>
       <c r="E43">
-        <v>-165.472</v>
+        <v>-159.264</v>
       </c>
       <c r="F43">
-        <v>254.528</v>
+        <v>260.736</v>
       </c>
       <c r="G43">
         <v>19.2</v>
@@ -4935,28 +4935,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M43">
-        <v>14.0753984</v>
+        <v>14.4187008</v>
       </c>
       <c r="N43">
-        <v>61.82460160000001</v>
+        <v>61.48129920000001</v>
       </c>
       <c r="O43">
-        <v>9.273690240000001</v>
+        <v>9.222194880000002</v>
       </c>
       <c r="P43">
-        <v>52.55091136000001</v>
+        <v>52.25910432000001</v>
       </c>
       <c r="Q43">
-        <v>70.15091136000001</v>
+        <v>69.85910432</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09692932791088492</v>
+        <v>0.09772773932903664</v>
       </c>
       <c r="T43">
-        <v>0.9364515965661508</v>
+        <v>0.951074782080108</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4973,7 +4973,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.392387330222924</v>
+        <v>5.263997155693806</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4981,22 +4981,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07642418881084125</v>
+        <v>0.07638802415426039</v>
       </c>
       <c r="C44">
-        <v>396.9793338986261</v>
+        <v>391.5262596713925</v>
       </c>
       <c r="D44">
-        <v>638.5153338986261</v>
+        <v>639.2702596713924</v>
       </c>
       <c r="E44">
-        <v>-159.264</v>
+        <v>-153.056</v>
       </c>
       <c r="F44">
-        <v>260.736</v>
+        <v>266.944</v>
       </c>
       <c r="G44">
         <v>19.2</v>
@@ -5017,28 +5017,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M44">
-        <v>14.4187008</v>
+        <v>14.7620032</v>
       </c>
       <c r="N44">
-        <v>61.48129920000001</v>
+        <v>61.13799680000001</v>
       </c>
       <c r="O44">
-        <v>9.222194880000002</v>
+        <v>9.170699520000001</v>
       </c>
       <c r="P44">
-        <v>52.25910432000001</v>
+        <v>51.96729728000001</v>
       </c>
       <c r="Q44">
-        <v>69.85910432</v>
+        <v>69.56729728000002</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09772773932903663</v>
+        <v>0.09855416518291296</v>
       </c>
       <c r="T44">
-        <v>0.9510747820801078</v>
+        <v>0.9662110618226248</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -5055,7 +5055,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.263997155693806</v>
+        <v>5.1415786171893</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5063,22 +5063,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07638802415426039</v>
+        <v>0.07635185949767953</v>
       </c>
       <c r="C45">
-        <v>391.5262596713925</v>
+        <v>386.0749726762139</v>
       </c>
       <c r="D45">
-        <v>639.2702596713924</v>
+        <v>640.0269726762139</v>
       </c>
       <c r="E45">
-        <v>-153.056</v>
+        <v>-146.848</v>
       </c>
       <c r="F45">
-        <v>266.944</v>
+        <v>273.152</v>
       </c>
       <c r="G45">
         <v>19.2</v>
@@ -5099,28 +5099,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M45">
-        <v>14.7620032</v>
+        <v>15.1053056</v>
       </c>
       <c r="N45">
-        <v>61.13799680000001</v>
+        <v>60.7946944</v>
       </c>
       <c r="O45">
-        <v>9.170699520000001</v>
+        <v>9.119204160000001</v>
       </c>
       <c r="P45">
-        <v>51.96729728000001</v>
+        <v>51.67549024</v>
       </c>
       <c r="Q45">
-        <v>69.56729728000002</v>
+        <v>69.27549024000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09855416518291296</v>
+        <v>0.09941010624585631</v>
       </c>
       <c r="T45">
-        <v>0.9662110618226248</v>
+        <v>0.9818879229845174</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.1415786171893</v>
+        <v>5.024724557707724</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5145,22 +5145,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07635185949767953</v>
+        <v>0.07631569484109868</v>
       </c>
       <c r="C46">
-        <v>386.0749726762139</v>
+        <v>380.6254792673254</v>
       </c>
       <c r="D46">
-        <v>640.0269726762139</v>
+        <v>640.7854792673254</v>
       </c>
       <c r="E46">
-        <v>-146.848</v>
+        <v>-140.64</v>
       </c>
       <c r="F46">
-        <v>273.152</v>
+        <v>279.36</v>
       </c>
       <c r="G46">
         <v>19.2</v>
@@ -5181,28 +5181,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M46">
-        <v>15.1053056</v>
+        <v>15.448608</v>
       </c>
       <c r="N46">
-        <v>60.7946944</v>
+        <v>60.45139200000001</v>
       </c>
       <c r="O46">
-        <v>9.119204160000001</v>
+        <v>9.0677088</v>
       </c>
       <c r="P46">
-        <v>51.67549024</v>
+        <v>51.38368320000001</v>
       </c>
       <c r="Q46">
-        <v>69.27549024000001</v>
+        <v>68.9836832</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09941010624585631</v>
+        <v>0.1002971724383612</v>
       </c>
       <c r="T46">
-        <v>0.9818879229845174</v>
+        <v>0.9981348518250244</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.024724557707724</v>
+        <v>4.913064011980885</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07631569484109868</v>
+        <v>0.07627953018451783</v>
       </c>
       <c r="C47">
-        <v>380.6254792673254</v>
+        <v>375.1777858291197</v>
       </c>
       <c r="D47">
-        <v>640.7854792673254</v>
+        <v>641.5457858291196</v>
       </c>
       <c r="E47">
-        <v>-140.64</v>
+        <v>-134.432</v>
       </c>
       <c r="F47">
-        <v>279.36</v>
+        <v>285.568</v>
       </c>
       <c r="G47">
         <v>19.2</v>
@@ -5263,28 +5263,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M47">
-        <v>15.448608</v>
+        <v>15.7919104</v>
       </c>
       <c r="N47">
-        <v>60.45139200000001</v>
+        <v>60.10808960000001</v>
       </c>
       <c r="O47">
-        <v>9.0677088</v>
+        <v>9.016213440000001</v>
       </c>
       <c r="P47">
-        <v>51.38368320000001</v>
+        <v>51.09187616000001</v>
       </c>
       <c r="Q47">
-        <v>68.9836832</v>
+        <v>68.69187616000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1002971724383612</v>
+        <v>0.1012170929342923</v>
       </c>
       <c r="T47">
-        <v>0.9981348518250244</v>
+        <v>1.014983518770735</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5301,7 +5301,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.913064011980885</v>
+        <v>4.806258272589996</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5309,22 +5309,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07627953018451783</v>
+        <v>0.07624336552793697</v>
       </c>
       <c r="C48">
-        <v>375.1777858291197</v>
+        <v>369.7318987763272</v>
       </c>
       <c r="D48">
-        <v>641.5457858291196</v>
+        <v>642.3078987763272</v>
       </c>
       <c r="E48">
-        <v>-134.432</v>
+        <v>-128.224</v>
       </c>
       <c r="F48">
-        <v>285.568</v>
+        <v>291.776</v>
       </c>
       <c r="G48">
         <v>19.2</v>
@@ -5345,28 +5345,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M48">
-        <v>15.7919104</v>
+        <v>16.1352128</v>
       </c>
       <c r="N48">
-        <v>60.10808960000001</v>
+        <v>59.7647872</v>
       </c>
       <c r="O48">
-        <v>9.016213440000001</v>
+        <v>8.964718079999999</v>
       </c>
       <c r="P48">
-        <v>51.09187616000001</v>
+        <v>50.80006912</v>
       </c>
       <c r="Q48">
-        <v>68.69187616000001</v>
+        <v>68.40006912000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1012170929342923</v>
+        <v>0.1021717274112018</v>
       </c>
       <c r="T48">
-        <v>1.014983518770735</v>
+        <v>1.032467984469114</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5383,7 +5383,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.806258272589996</v>
+        <v>4.70399745827957</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5391,22 +5391,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07624336552793697</v>
+        <v>0.07620720087135611</v>
       </c>
       <c r="C49">
-        <v>369.7318987763272</v>
+        <v>364.2878245541943</v>
       </c>
       <c r="D49">
-        <v>642.3078987763272</v>
+        <v>643.0718245541942</v>
       </c>
       <c r="E49">
-        <v>-128.224</v>
+        <v>-122.016</v>
       </c>
       <c r="F49">
-        <v>291.776</v>
+        <v>297.984</v>
       </c>
       <c r="G49">
         <v>19.2</v>
@@ -5427,28 +5427,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M49">
-        <v>16.1352128</v>
+        <v>16.4785152</v>
       </c>
       <c r="N49">
-        <v>59.7647872</v>
+        <v>59.4214848</v>
       </c>
       <c r="O49">
-        <v>8.964718079999999</v>
+        <v>8.91322272</v>
       </c>
       <c r="P49">
-        <v>50.80006912</v>
+        <v>50.50826208</v>
       </c>
       <c r="Q49">
-        <v>68.40006912000001</v>
+        <v>68.10826208</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1021717274112018</v>
+        <v>0.1031630785987618</v>
       </c>
       <c r="T49">
-        <v>1.032467984469114</v>
+        <v>1.050624929617431</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.70399745827957</v>
+        <v>4.60599751123208</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5473,22 +5473,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07620720087135611</v>
+        <v>0.07617103621477525</v>
       </c>
       <c r="C50">
-        <v>364.2878245541943</v>
+        <v>358.845569638668</v>
       </c>
       <c r="D50">
-        <v>643.0718245541942</v>
+        <v>643.8375696386679</v>
       </c>
       <c r="E50">
-        <v>-122.016</v>
+        <v>-115.808</v>
       </c>
       <c r="F50">
-        <v>297.984</v>
+        <v>304.192</v>
       </c>
       <c r="G50">
         <v>19.2</v>
@@ -5509,28 +5509,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M50">
-        <v>16.4785152</v>
+        <v>16.8218176</v>
       </c>
       <c r="N50">
-        <v>59.4214848</v>
+        <v>59.0781824</v>
       </c>
       <c r="O50">
-        <v>8.91322272</v>
+        <v>8.86172736</v>
       </c>
       <c r="P50">
-        <v>50.50826208</v>
+        <v>50.21645504</v>
       </c>
       <c r="Q50">
-        <v>68.10826208</v>
+        <v>67.81645503999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1031630785987618</v>
+        <v>0.1041933063034809</v>
       </c>
       <c r="T50">
-        <v>1.050624929617431</v>
+        <v>1.069493911830388</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5547,7 +5547,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.60599751123208</v>
+        <v>4.511997562023263</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5555,22 +5555,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07617103621477525</v>
+        <v>0.07719737155819441</v>
       </c>
       <c r="C51">
-        <v>358.845569638668</v>
+        <v>331.591436782722</v>
       </c>
       <c r="D51">
-        <v>643.8375696386679</v>
+        <v>622.7914367827219</v>
       </c>
       <c r="E51">
-        <v>-115.808</v>
+        <v>-109.6</v>
       </c>
       <c r="F51">
-        <v>304.192</v>
+        <v>310.4</v>
       </c>
       <c r="G51">
         <v>19.2</v>
@@ -5591,45 +5591,45 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M51">
-        <v>16.8218176</v>
+        <v>17.94112</v>
       </c>
       <c r="N51">
-        <v>59.0781824</v>
+        <v>57.95888000000001</v>
       </c>
       <c r="O51">
-        <v>8.86172736</v>
+        <v>8.693832</v>
       </c>
       <c r="P51">
-        <v>50.21645504</v>
+        <v>49.26504800000001</v>
       </c>
       <c r="Q51">
-        <v>67.81645503999999</v>
+        <v>66.865048</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1041933063034809</v>
+        <v>0.1052647431163888</v>
       </c>
       <c r="T51">
-        <v>1.069493911830388</v>
+        <v>1.089117653331863</v>
       </c>
       <c r="U51">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V51">
         <v>0.15</v>
       </c>
       <c r="W51">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y51">
-        <v>4.511997562023263</v>
+        <v>4.230505118966931</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5637,22 +5637,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07719737155819441</v>
+        <v>0.07718245690161354</v>
       </c>
       <c r="C52">
-        <v>331.591436782722</v>
+        <v>325.6794212695401</v>
       </c>
       <c r="D52">
-        <v>622.7914367827219</v>
+        <v>623.0874212695401</v>
       </c>
       <c r="E52">
-        <v>-109.6</v>
+        <v>-103.392</v>
       </c>
       <c r="F52">
-        <v>310.4</v>
+        <v>316.608</v>
       </c>
       <c r="G52">
         <v>19.2</v>
@@ -5673,28 +5673,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M52">
-        <v>17.94112</v>
+        <v>18.2999424</v>
       </c>
       <c r="N52">
-        <v>57.95888000000001</v>
+        <v>57.6000576</v>
       </c>
       <c r="O52">
-        <v>8.693832</v>
+        <v>8.64000864</v>
       </c>
       <c r="P52">
-        <v>49.26504800000001</v>
+        <v>48.96004896</v>
       </c>
       <c r="Q52">
-        <v>66.865048</v>
+        <v>66.56004896</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1052647431163888</v>
+        <v>0.1063799120441093</v>
       </c>
       <c r="T52">
-        <v>1.089117653331863</v>
+        <v>1.109542363874215</v>
       </c>
       <c r="U52">
         <v>0.0578</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.230505118966931</v>
+        <v>4.147554038202873</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5719,22 +5719,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07718245690161354</v>
+        <v>0.07716754224503268</v>
       </c>
       <c r="C53">
-        <v>325.6794212695401</v>
+        <v>319.767687226098</v>
       </c>
       <c r="D53">
-        <v>623.0874212695401</v>
+        <v>623.3836872260979</v>
       </c>
       <c r="E53">
-        <v>-103.392</v>
+        <v>-97.18400000000003</v>
       </c>
       <c r="F53">
-        <v>316.608</v>
+        <v>322.816</v>
       </c>
       <c r="G53">
         <v>19.2</v>
@@ -5755,28 +5755,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M53">
-        <v>18.2999424</v>
+        <v>18.6587648</v>
       </c>
       <c r="N53">
-        <v>57.6000576</v>
+        <v>57.24123520000001</v>
       </c>
       <c r="O53">
-        <v>8.64000864</v>
+        <v>8.58618528</v>
       </c>
       <c r="P53">
-        <v>48.96004896</v>
+        <v>48.65504992</v>
       </c>
       <c r="Q53">
-        <v>66.56004896</v>
+        <v>66.25504992</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1063799120441093</v>
+        <v>0.1075415463438181</v>
       </c>
       <c r="T53">
-        <v>1.109542363874215</v>
+        <v>1.130818104022498</v>
       </c>
       <c r="U53">
         <v>0.0578</v>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.147554038202873</v>
+        <v>4.06779338362205</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5801,22 +5801,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07716754224503268</v>
+        <v>0.07872937758845183</v>
       </c>
       <c r="C54">
-        <v>319.767687226098</v>
+        <v>283.992694269568</v>
       </c>
       <c r="D54">
-        <v>623.3836872260979</v>
+        <v>593.816694269568</v>
       </c>
       <c r="E54">
-        <v>-97.18400000000003</v>
+        <v>-90.976</v>
       </c>
       <c r="F54">
-        <v>322.816</v>
+        <v>329.024</v>
       </c>
       <c r="G54">
         <v>19.2</v>
@@ -5837,45 +5837,45 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M54">
-        <v>18.6587648</v>
+        <v>20.1691712</v>
       </c>
       <c r="N54">
-        <v>57.24123520000001</v>
+        <v>55.7308288</v>
       </c>
       <c r="O54">
-        <v>8.58618528</v>
+        <v>8.35962432</v>
       </c>
       <c r="P54">
-        <v>48.65504992</v>
+        <v>47.37120448</v>
       </c>
       <c r="Q54">
-        <v>66.25504992</v>
+        <v>64.97120448000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1075415463438181</v>
+        <v>0.108752611890323</v>
       </c>
       <c r="T54">
-        <v>1.130818104022498</v>
+        <v>1.152999194815388</v>
       </c>
       <c r="U54">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V54">
         <v>0.15</v>
       </c>
       <c r="W54">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y54">
-        <v>4.06779338362205</v>
+        <v>3.763169009145998</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5883,22 +5883,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07872937758845183</v>
+        <v>0.07874421293187098</v>
       </c>
       <c r="C55">
-        <v>283.992694269568</v>
+        <v>277.5172884400304</v>
       </c>
       <c r="D55">
-        <v>593.816694269568</v>
+        <v>593.5492884400303</v>
       </c>
       <c r="E55">
-        <v>-90.976</v>
+        <v>-84.76800000000003</v>
       </c>
       <c r="F55">
-        <v>329.024</v>
+        <v>335.232</v>
       </c>
       <c r="G55">
         <v>19.2</v>
@@ -5919,28 +5919,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M55">
-        <v>20.1691712</v>
+        <v>20.5497216</v>
       </c>
       <c r="N55">
-        <v>55.7308288</v>
+        <v>55.35027840000001</v>
       </c>
       <c r="O55">
-        <v>8.35962432</v>
+        <v>8.30254176</v>
       </c>
       <c r="P55">
-        <v>47.37120448</v>
+        <v>47.04773664000001</v>
       </c>
       <c r="Q55">
-        <v>64.97120448000001</v>
+        <v>64.64773664000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.108752611890323</v>
+        <v>0.1100163324605891</v>
       </c>
       <c r="T55">
-        <v>1.152999194815388</v>
+        <v>1.176144680860144</v>
       </c>
       <c r="U55">
         <v>0.0613</v>
@@ -5957,7 +5957,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.763169009145998</v>
+        <v>3.693480694161813</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5965,22 +5965,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07874421293187098</v>
+        <v>0.07875904827529012</v>
       </c>
       <c r="C56">
-        <v>277.5172884400304</v>
+        <v>271.042123336941</v>
       </c>
       <c r="D56">
-        <v>593.5492884400303</v>
+        <v>593.2821233369409</v>
       </c>
       <c r="E56">
-        <v>-84.76800000000003</v>
+        <v>-78.56</v>
       </c>
       <c r="F56">
-        <v>335.232</v>
+        <v>341.44</v>
       </c>
       <c r="G56">
         <v>19.2</v>
@@ -6001,28 +6001,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M56">
-        <v>20.5497216</v>
+        <v>20.930272</v>
       </c>
       <c r="N56">
-        <v>55.35027840000001</v>
+        <v>54.969728</v>
       </c>
       <c r="O56">
-        <v>8.30254176</v>
+        <v>8.245459200000001</v>
       </c>
       <c r="P56">
-        <v>47.04773664000001</v>
+        <v>46.7242688</v>
       </c>
       <c r="Q56">
-        <v>64.64773664000001</v>
+        <v>64.3242688</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1100163324605891</v>
+        <v>0.1113362183895336</v>
       </c>
       <c r="T56">
-        <v>1.176144680860144</v>
+        <v>1.200318855173555</v>
       </c>
       <c r="U56">
         <v>0.0613</v>
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.693480694161813</v>
+        <v>3.626326499722508</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6047,22 +6047,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07875904827529012</v>
+        <v>0.07877388361870925</v>
       </c>
       <c r="C57">
-        <v>271.042123336941</v>
+        <v>264.5671986353829</v>
       </c>
       <c r="D57">
-        <v>593.2821233369409</v>
+        <v>593.0151986353828</v>
       </c>
       <c r="E57">
-        <v>-78.56</v>
+        <v>-72.35199999999998</v>
       </c>
       <c r="F57">
-        <v>341.44</v>
+        <v>347.648</v>
       </c>
       <c r="G57">
         <v>19.2</v>
@@ -6083,28 +6083,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M57">
-        <v>20.930272</v>
+        <v>21.3108224</v>
       </c>
       <c r="N57">
-        <v>54.969728</v>
+        <v>54.5891776</v>
       </c>
       <c r="O57">
-        <v>8.245459200000001</v>
+        <v>8.18837664</v>
       </c>
       <c r="P57">
-        <v>46.7242688</v>
+        <v>46.40080096</v>
       </c>
       <c r="Q57">
-        <v>64.3242688</v>
+        <v>64.00080095999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1113362183895336</v>
+        <v>0.1127160991334301</v>
       </c>
       <c r="T57">
-        <v>1.200318855173555</v>
+        <v>1.225591855592121</v>
       </c>
       <c r="U57">
         <v>0.0613</v>
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.626326499722508</v>
+        <v>3.561570669370319</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6129,22 +6129,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07877388361870925</v>
+        <v>0.08014531896212841</v>
       </c>
       <c r="C58">
-        <v>264.5671986353829</v>
+        <v>234.6796397560469</v>
       </c>
       <c r="D58">
-        <v>593.0151986353828</v>
+        <v>569.3356397560468</v>
       </c>
       <c r="E58">
-        <v>-72.35199999999998</v>
+        <v>-66.14400000000001</v>
       </c>
       <c r="F58">
-        <v>347.648</v>
+        <v>353.856</v>
       </c>
       <c r="G58">
         <v>19.2</v>
@@ -6165,45 +6165,45 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M58">
-        <v>21.3108224</v>
+        <v>22.6821696</v>
       </c>
       <c r="N58">
-        <v>54.5891776</v>
+        <v>53.2178304</v>
       </c>
       <c r="O58">
-        <v>8.18837664</v>
+        <v>7.98267456</v>
       </c>
       <c r="P58">
-        <v>46.40080096</v>
+        <v>45.23515584</v>
       </c>
       <c r="Q58">
-        <v>64.00080095999999</v>
+        <v>62.83515584000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1127160991334301</v>
+        <v>0.1141601603770428</v>
       </c>
       <c r="T58">
-        <v>1.225591855592121</v>
+        <v>1.252040344402249</v>
       </c>
       <c r="U58">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V58">
         <v>0.15</v>
       </c>
       <c r="W58">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y58">
-        <v>3.561570669370319</v>
+        <v>3.34624074056831</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6211,22 +6211,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08014531896212841</v>
+        <v>0.08018395430554756</v>
       </c>
       <c r="C59">
-        <v>234.6796397560469</v>
+        <v>227.8319088581033</v>
       </c>
       <c r="D59">
-        <v>569.3356397560468</v>
+        <v>568.6959088581033</v>
       </c>
       <c r="E59">
-        <v>-66.14400000000001</v>
+        <v>-59.93599999999998</v>
       </c>
       <c r="F59">
-        <v>353.856</v>
+        <v>360.064</v>
       </c>
       <c r="G59">
         <v>19.2</v>
@@ -6247,28 +6247,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M59">
-        <v>22.6821696</v>
+        <v>23.0801024</v>
       </c>
       <c r="N59">
-        <v>53.2178304</v>
+        <v>52.8198976</v>
       </c>
       <c r="O59">
-        <v>7.98267456</v>
+        <v>7.92298464</v>
       </c>
       <c r="P59">
-        <v>45.23515584</v>
+        <v>44.89691296</v>
       </c>
       <c r="Q59">
-        <v>62.83515584000001</v>
+        <v>62.49691296</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1141601603770428</v>
+        <v>0.1156729864417799</v>
       </c>
       <c r="T59">
-        <v>1.252040344402249</v>
+        <v>1.279748285060478</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6285,7 +6285,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.34624074056831</v>
+        <v>3.288546934696442</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08018395430554755</v>
+        <v>0.0802225896489667</v>
       </c>
       <c r="C60">
-        <v>227.8319088581036</v>
+        <v>220.9856140068487</v>
       </c>
       <c r="D60">
-        <v>568.6959088581035</v>
+        <v>568.0576140068486</v>
       </c>
       <c r="E60">
-        <v>-59.93600000000004</v>
+        <v>-53.72800000000007</v>
       </c>
       <c r="F60">
-        <v>360.064</v>
+        <v>366.2719999999999</v>
       </c>
       <c r="G60">
         <v>19.2</v>
@@ -6329,28 +6329,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M60">
-        <v>23.0801024</v>
+        <v>23.4780352</v>
       </c>
       <c r="N60">
-        <v>52.8198976</v>
+        <v>52.42196480000001</v>
       </c>
       <c r="O60">
-        <v>7.92298464</v>
+        <v>7.863294720000002</v>
       </c>
       <c r="P60">
-        <v>44.89691296</v>
+        <v>44.55867008000001</v>
       </c>
       <c r="Q60">
-        <v>62.49691296</v>
+        <v>62.15867008000001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1156729864417799</v>
+        <v>0.1172596088999188</v>
       </c>
       <c r="T60">
-        <v>1.279748285060477</v>
+        <v>1.308807832580083</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6367,7 +6367,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.288546934696443</v>
+        <v>3.23280885105752</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6375,22 +6375,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.0802225896489667</v>
+        <v>0.08026122499238583</v>
       </c>
       <c r="C61">
-        <v>220.9856140068487</v>
+        <v>214.1407503723186</v>
       </c>
       <c r="D61">
-        <v>568.0576140068486</v>
+        <v>567.4207503723185</v>
       </c>
       <c r="E61">
-        <v>-53.72800000000007</v>
+        <v>-47.52000000000004</v>
       </c>
       <c r="F61">
-        <v>366.2719999999999</v>
+        <v>372.48</v>
       </c>
       <c r="G61">
         <v>19.2</v>
@@ -6411,28 +6411,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M61">
-        <v>23.4780352</v>
+        <v>23.875968</v>
       </c>
       <c r="N61">
-        <v>52.42196480000001</v>
+        <v>52.02403200000001</v>
       </c>
       <c r="O61">
-        <v>7.863294720000002</v>
+        <v>7.8036048</v>
       </c>
       <c r="P61">
-        <v>44.55867008000001</v>
+        <v>44.2204272</v>
       </c>
       <c r="Q61">
-        <v>62.15867008000001</v>
+        <v>61.8204272</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1172596088999188</v>
+        <v>0.1189255624809646</v>
       </c>
       <c r="T61">
-        <v>1.308807832580083</v>
+        <v>1.339320357475669</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6449,7 +6449,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.23280885105752</v>
+        <v>3.178928703539894</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6457,22 +6457,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08026122499238583</v>
+        <v>0.08029986033580498</v>
       </c>
       <c r="C62">
-        <v>214.1407503723186</v>
+        <v>207.2973131461848</v>
       </c>
       <c r="D62">
-        <v>567.4207503723185</v>
+        <v>566.7853131461848</v>
       </c>
       <c r="E62">
-        <v>-47.52000000000004</v>
+        <v>-41.31200000000001</v>
       </c>
       <c r="F62">
-        <v>372.48</v>
+        <v>378.688</v>
       </c>
       <c r="G62">
         <v>19.2</v>
@@ -6493,28 +6493,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M62">
-        <v>23.875968</v>
+        <v>24.2739008</v>
       </c>
       <c r="N62">
-        <v>52.02403200000001</v>
+        <v>51.62609920000001</v>
       </c>
       <c r="O62">
-        <v>7.8036048</v>
+        <v>7.74391488</v>
       </c>
       <c r="P62">
-        <v>44.2204272</v>
+        <v>43.88218432000001</v>
       </c>
       <c r="Q62">
-        <v>61.8204272</v>
+        <v>61.48218432000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1189255624809646</v>
+        <v>0.1206769495789871</v>
       </c>
       <c r="T62">
-        <v>1.339320357475669</v>
+        <v>1.371397627237696</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.178928703539894</v>
+        <v>3.126815118235962</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6539,22 +6539,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08029986033580498</v>
+        <v>0.08033849567922413</v>
       </c>
       <c r="C63">
-        <v>207.2973131461848</v>
+        <v>200.4552975416342</v>
       </c>
       <c r="D63">
-        <v>566.7853131461848</v>
+        <v>566.1512975416341</v>
       </c>
       <c r="E63">
-        <v>-41.31200000000001</v>
+        <v>-35.10400000000004</v>
       </c>
       <c r="F63">
-        <v>378.688</v>
+        <v>384.896</v>
       </c>
       <c r="G63">
         <v>19.2</v>
@@ -6575,28 +6575,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M63">
-        <v>24.2739008</v>
+        <v>24.6718336</v>
       </c>
       <c r="N63">
-        <v>51.62609920000001</v>
+        <v>51.22816640000001</v>
       </c>
       <c r="O63">
-        <v>7.74391488</v>
+        <v>7.684224960000001</v>
       </c>
       <c r="P63">
-        <v>43.88218432000001</v>
+        <v>43.54394144</v>
       </c>
       <c r="Q63">
-        <v>61.48218432000001</v>
+        <v>61.14394144000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1206769495789871</v>
+        <v>0.1225205149453266</v>
       </c>
       <c r="T63">
-        <v>1.371397627237696</v>
+        <v>1.405163174355619</v>
       </c>
       <c r="U63">
         <v>0.0641</v>
@@ -6613,7 +6613,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.126815118235962</v>
+        <v>3.07638261632893</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6621,22 +6621,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08033849567922413</v>
+        <v>0.08037713102264327</v>
       </c>
       <c r="C64">
-        <v>200.4552975416342</v>
+        <v>193.6146987932479</v>
       </c>
       <c r="D64">
-        <v>566.1512975416341</v>
+        <v>565.5186987932478</v>
       </c>
       <c r="E64">
-        <v>-35.10400000000004</v>
+        <v>-28.89600000000002</v>
       </c>
       <c r="F64">
-        <v>384.896</v>
+        <v>391.104</v>
       </c>
       <c r="G64">
         <v>19.2</v>
@@ -6657,28 +6657,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M64">
-        <v>24.6718336</v>
+        <v>25.0697664</v>
       </c>
       <c r="N64">
-        <v>51.22816640000001</v>
+        <v>50.8302336</v>
       </c>
       <c r="O64">
-        <v>7.684224960000001</v>
+        <v>7.62453504</v>
       </c>
       <c r="P64">
-        <v>43.54394144</v>
+        <v>43.20569856</v>
       </c>
       <c r="Q64">
-        <v>61.14394144000001</v>
+        <v>60.80569856</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1225205149453266</v>
+        <v>0.1244637324936305</v>
       </c>
       <c r="T64">
-        <v>1.405163174355619</v>
+        <v>1.440753886182618</v>
       </c>
       <c r="U64">
         <v>0.0641</v>
@@ -6695,7 +6695,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.07638261632893</v>
+        <v>3.027551146228471</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6703,22 +6703,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08037713102264327</v>
+        <v>0.0846589663660624</v>
       </c>
       <c r="C65">
-        <v>193.6146987932479</v>
+        <v>125.0926905140128</v>
       </c>
       <c r="D65">
-        <v>565.5186987932478</v>
+        <v>503.2046905140127</v>
       </c>
       <c r="E65">
-        <v>-28.89600000000002</v>
+        <v>-22.68800000000005</v>
       </c>
       <c r="F65">
-        <v>391.104</v>
+        <v>397.312</v>
       </c>
       <c r="G65">
         <v>19.2</v>
@@ -6739,45 +6739,45 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M65">
-        <v>25.0697664</v>
+        <v>28.5667328</v>
       </c>
       <c r="N65">
-        <v>50.8302336</v>
+        <v>47.33326720000001</v>
       </c>
       <c r="O65">
-        <v>7.62453504</v>
+        <v>7.099990080000001</v>
       </c>
       <c r="P65">
-        <v>43.20569856</v>
+        <v>40.23327712000001</v>
       </c>
       <c r="Q65">
-        <v>60.80569856</v>
+        <v>57.83327712000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1244637324936305</v>
+        <v>0.1265149065723956</v>
       </c>
       <c r="T65">
-        <v>1.440753886182618</v>
+        <v>1.478321859777784</v>
       </c>
       <c r="U65">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V65">
         <v>0.15</v>
       </c>
       <c r="W65">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y65">
-        <v>3.027551146228471</v>
+        <v>2.656936672856058</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6785,22 +6785,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.0846589663660624</v>
+        <v>0.08476390170948156</v>
       </c>
       <c r="C66">
-        <v>125.0926905140128</v>
+        <v>117.5294885272373</v>
       </c>
       <c r="D66">
-        <v>503.2046905140127</v>
+        <v>501.8494885272372</v>
       </c>
       <c r="E66">
-        <v>-22.68800000000005</v>
+        <v>-16.48000000000002</v>
       </c>
       <c r="F66">
-        <v>397.312</v>
+        <v>403.52</v>
       </c>
       <c r="G66">
         <v>19.2</v>
@@ -6821,28 +6821,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M66">
-        <v>28.5667328</v>
+        <v>29.013088</v>
       </c>
       <c r="N66">
-        <v>47.33326720000001</v>
+        <v>46.88691200000001</v>
       </c>
       <c r="O66">
-        <v>7.099990080000001</v>
+        <v>7.033036800000001</v>
       </c>
       <c r="P66">
-        <v>40.23327712000001</v>
+        <v>39.8538752</v>
       </c>
       <c r="Q66">
-        <v>57.83327712000001</v>
+        <v>57.45387520000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1265149065723956</v>
+        <v>0.1286832905985188</v>
       </c>
       <c r="T66">
-        <v>1.478321859777784</v>
+        <v>1.518036574721246</v>
       </c>
       <c r="U66">
         <v>0.07190000000000001</v>
@@ -6859,7 +6859,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.656936672856058</v>
+        <v>2.616060724042887</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6867,22 +6867,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08476390170948156</v>
+        <v>0.08486883705290071</v>
       </c>
       <c r="C67">
-        <v>117.5294885272373</v>
+        <v>109.9735664390515</v>
       </c>
       <c r="D67">
-        <v>501.8494885272372</v>
+        <v>500.5015664390515</v>
       </c>
       <c r="E67">
-        <v>-16.48000000000002</v>
+        <v>-10.27199999999999</v>
       </c>
       <c r="F67">
-        <v>403.52</v>
+        <v>409.728</v>
       </c>
       <c r="G67">
         <v>19.2</v>
@@ -6903,28 +6903,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M67">
-        <v>29.013088</v>
+        <v>29.4594432</v>
       </c>
       <c r="N67">
-        <v>46.88691200000001</v>
+        <v>46.4405568</v>
       </c>
       <c r="O67">
-        <v>7.033036800000001</v>
+        <v>6.966083520000001</v>
       </c>
       <c r="P67">
-        <v>39.8538752</v>
+        <v>39.47447328000001</v>
       </c>
       <c r="Q67">
-        <v>57.45387520000001</v>
+        <v>57.07447328000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1286832905985188</v>
+        <v>0.1309792266261786</v>
       </c>
       <c r="T67">
-        <v>1.518036574721246</v>
+        <v>1.560087449367264</v>
       </c>
       <c r="U67">
         <v>0.07190000000000001</v>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.616060724042887</v>
+        <v>2.576423440345267</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6949,22 +6949,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08486883705290071</v>
+        <v>0.08497377239631984</v>
       </c>
       <c r="C68">
-        <v>109.9735664390515</v>
+        <v>102.4248657471512</v>
       </c>
       <c r="D68">
-        <v>500.5015664390515</v>
+        <v>499.1608657471511</v>
       </c>
       <c r="E68">
-        <v>-10.27199999999999</v>
+        <v>-4.064000000000021</v>
       </c>
       <c r="F68">
-        <v>409.728</v>
+        <v>415.936</v>
       </c>
       <c r="G68">
         <v>19.2</v>
@@ -6985,28 +6985,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M68">
-        <v>29.4594432</v>
+        <v>29.9057984</v>
       </c>
       <c r="N68">
-        <v>46.4405568</v>
+        <v>45.9942016</v>
       </c>
       <c r="O68">
-        <v>6.966083520000001</v>
+        <v>6.899130240000001</v>
       </c>
       <c r="P68">
-        <v>39.47447328000001</v>
+        <v>39.09507136000001</v>
       </c>
       <c r="Q68">
-        <v>57.07447328000001</v>
+        <v>56.69507136000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1309792266261786</v>
+        <v>0.1334143102918783</v>
       </c>
       <c r="T68">
-        <v>1.560087449367264</v>
+        <v>1.604686861870616</v>
       </c>
       <c r="U68">
         <v>0.07190000000000001</v>
@@ -7023,7 +7023,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.576423440345267</v>
+        <v>2.537969359146085</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7031,22 +7031,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08497377239631984</v>
+        <v>0.085078707739739</v>
       </c>
       <c r="C69">
-        <v>102.4248657471512</v>
+        <v>94.8833285743998</v>
       </c>
       <c r="D69">
-        <v>499.1608657471511</v>
+        <v>497.8273285743998</v>
       </c>
       <c r="E69">
-        <v>-4.064000000000021</v>
+        <v>2.144000000000005</v>
       </c>
       <c r="F69">
-        <v>415.936</v>
+        <v>422.144</v>
       </c>
       <c r="G69">
         <v>19.2</v>
@@ -7067,28 +7067,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M69">
-        <v>29.9057984</v>
+        <v>30.3521536</v>
       </c>
       <c r="N69">
-        <v>45.9942016</v>
+        <v>45.5478464</v>
       </c>
       <c r="O69">
-        <v>6.899130240000001</v>
+        <v>6.832176960000001</v>
       </c>
       <c r="P69">
-        <v>39.09507136000001</v>
+        <v>38.71566944000001</v>
       </c>
       <c r="Q69">
-        <v>56.69507136000001</v>
+        <v>56.31566944000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1334143102918783</v>
+        <v>0.1360015866866844</v>
       </c>
       <c r="T69">
-        <v>1.604686861870616</v>
+        <v>1.652073737655428</v>
       </c>
       <c r="U69">
         <v>0.07190000000000001</v>
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.537969359146085</v>
+        <v>2.500646280335113</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7113,22 +7113,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.085078707739739</v>
+        <v>0.08747099308315814</v>
       </c>
       <c r="C70">
-        <v>94.8833285743998</v>
+        <v>60.09561559934752</v>
       </c>
       <c r="D70">
-        <v>497.8273285743998</v>
+        <v>469.2476155993476</v>
       </c>
       <c r="E70">
-        <v>2.144000000000005</v>
+        <v>8.352000000000032</v>
       </c>
       <c r="F70">
-        <v>422.144</v>
+        <v>428.352</v>
       </c>
       <c r="G70">
         <v>19.2</v>
@@ -7149,45 +7149,45 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M70">
-        <v>30.3521536</v>
+        <v>32.4690816</v>
       </c>
       <c r="N70">
-        <v>45.5478464</v>
+        <v>43.4309184</v>
       </c>
       <c r="O70">
-        <v>6.832176960000001</v>
+        <v>6.51463776</v>
       </c>
       <c r="P70">
-        <v>38.71566944000001</v>
+        <v>36.91628064</v>
       </c>
       <c r="Q70">
-        <v>56.31566944000001</v>
+        <v>54.51628064000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1360015866866844</v>
+        <v>0.1387557841392198</v>
       </c>
       <c r="T70">
-        <v>1.652073737655428</v>
+        <v>1.702517831232808</v>
       </c>
       <c r="U70">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V70">
         <v>0.15</v>
       </c>
       <c r="W70">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y70">
-        <v>2.500646280335113</v>
+        <v>2.337608465032778</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7195,22 +7195,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08747099308315814</v>
+        <v>0.08760907842657728</v>
       </c>
       <c r="C71">
-        <v>60.09561559934752</v>
+        <v>52.33780343923411</v>
       </c>
       <c r="D71">
-        <v>469.2476155993476</v>
+        <v>467.6978034392341</v>
       </c>
       <c r="E71">
-        <v>8.352000000000032</v>
+        <v>14.56</v>
       </c>
       <c r="F71">
-        <v>428.352</v>
+        <v>434.56</v>
       </c>
       <c r="G71">
         <v>19.2</v>
@@ -7231,28 +7231,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M71">
-        <v>32.4690816</v>
+        <v>32.93964800000001</v>
       </c>
       <c r="N71">
-        <v>43.4309184</v>
+        <v>42.960352</v>
       </c>
       <c r="O71">
-        <v>6.51463776</v>
+        <v>6.4440528</v>
       </c>
       <c r="P71">
-        <v>36.91628064</v>
+        <v>36.5162992</v>
       </c>
       <c r="Q71">
-        <v>54.51628064000001</v>
+        <v>54.1162992</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1387557841392198</v>
+        <v>0.1416935947552576</v>
       </c>
       <c r="T71">
-        <v>1.702517831232808</v>
+        <v>1.756324864382014</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.337608465032778</v>
+        <v>2.304214058389452</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7277,22 +7277,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08760907842657728</v>
+        <v>0.08774716376999643</v>
       </c>
       <c r="C72">
-        <v>52.33780343923411</v>
+        <v>44.59019489362646</v>
       </c>
       <c r="D72">
-        <v>467.6978034392341</v>
+        <v>466.1581948936265</v>
       </c>
       <c r="E72">
-        <v>14.56</v>
+        <v>20.76800000000003</v>
       </c>
       <c r="F72">
-        <v>434.56</v>
+        <v>440.768</v>
       </c>
       <c r="G72">
         <v>19.2</v>
@@ -7313,28 +7313,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M72">
-        <v>32.93964800000001</v>
+        <v>33.41021440000001</v>
       </c>
       <c r="N72">
-        <v>42.960352</v>
+        <v>42.4897856</v>
       </c>
       <c r="O72">
-        <v>6.4440528</v>
+        <v>6.373467839999999</v>
       </c>
       <c r="P72">
-        <v>36.5162992</v>
+        <v>36.11631776</v>
       </c>
       <c r="Q72">
-        <v>54.1162992</v>
+        <v>53.71631776</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1416935947552576</v>
+        <v>0.1448340129999877</v>
       </c>
       <c r="T72">
-        <v>1.756324864382014</v>
+        <v>1.813842727403579</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7351,7 +7351,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.304214058389452</v>
+        <v>2.271760339257206</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7359,22 +7359,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08774716376999642</v>
+        <v>0.08788524911341557</v>
       </c>
       <c r="C73">
-        <v>44.59019489362663</v>
+        <v>36.85268952569913</v>
       </c>
       <c r="D73">
-        <v>466.1581948936266</v>
+        <v>464.6286895256991</v>
       </c>
       <c r="E73">
-        <v>20.76799999999997</v>
+        <v>26.97599999999994</v>
       </c>
       <c r="F73">
-        <v>440.768</v>
+        <v>446.9759999999999</v>
       </c>
       <c r="G73">
         <v>19.2</v>
@@ -7395,28 +7395,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M73">
-        <v>33.4102144</v>
+        <v>33.8807808</v>
       </c>
       <c r="N73">
-        <v>42.4897856</v>
+        <v>42.01921920000001</v>
       </c>
       <c r="O73">
-        <v>6.373467840000001</v>
+        <v>6.302882880000001</v>
       </c>
       <c r="P73">
-        <v>36.11631776</v>
+        <v>35.71633632000001</v>
       </c>
       <c r="Q73">
-        <v>53.71631776</v>
+        <v>53.31633632000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1448340129999877</v>
+        <v>0.148198746833627</v>
       </c>
       <c r="T73">
-        <v>1.813842727403578</v>
+        <v>1.875469009212397</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7433,7 +7433,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.271760339257206</v>
+        <v>2.240208112323079</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7441,22 +7441,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08788524911341557</v>
+        <v>0.08802333445683472</v>
       </c>
       <c r="C74">
-        <v>36.85268952569913</v>
+        <v>29.12518821248244</v>
       </c>
       <c r="D74">
-        <v>464.6286895256991</v>
+        <v>463.1091882124824</v>
       </c>
       <c r="E74">
-        <v>26.97599999999994</v>
+        <v>33.18399999999997</v>
       </c>
       <c r="F74">
-        <v>446.9759999999999</v>
+        <v>453.184</v>
       </c>
       <c r="G74">
         <v>19.2</v>
@@ -7477,28 +7477,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M74">
-        <v>33.8807808</v>
+        <v>34.3513472</v>
       </c>
       <c r="N74">
-        <v>42.01921920000001</v>
+        <v>41.54865280000001</v>
       </c>
       <c r="O74">
-        <v>6.302882880000001</v>
+        <v>6.232297920000001</v>
       </c>
       <c r="P74">
-        <v>35.71633632000001</v>
+        <v>35.31635488000001</v>
       </c>
       <c r="Q74">
-        <v>53.31633632000001</v>
+        <v>52.91635488000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.148198746833627</v>
+        <v>0.1518127202104989</v>
       </c>
       <c r="T74">
-        <v>1.875469009212397</v>
+        <v>1.941660200784833</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.240208112323079</v>
+        <v>2.209520329962489</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7523,22 +7523,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08802333445683472</v>
+        <v>0.08816141980025385</v>
       </c>
       <c r="C75">
-        <v>29.12518821248244</v>
+        <v>21.40759312345068</v>
       </c>
       <c r="D75">
-        <v>463.1091882124824</v>
+        <v>461.5995931234506</v>
       </c>
       <c r="E75">
-        <v>33.18399999999997</v>
+        <v>39.39199999999994</v>
       </c>
       <c r="F75">
-        <v>453.184</v>
+        <v>459.3919999999999</v>
       </c>
       <c r="G75">
         <v>19.2</v>
@@ -7559,28 +7559,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M75">
-        <v>34.3513472</v>
+        <v>34.82191359999999</v>
       </c>
       <c r="N75">
-        <v>41.54865280000001</v>
+        <v>41.07808640000001</v>
       </c>
       <c r="O75">
-        <v>6.232297920000001</v>
+        <v>6.161712960000002</v>
       </c>
       <c r="P75">
-        <v>35.31635488000001</v>
+        <v>34.91637344000001</v>
       </c>
       <c r="Q75">
-        <v>52.91635488000001</v>
+        <v>52.51637344000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1518127202104989</v>
+        <v>0.1557046915394379</v>
       </c>
       <c r="T75">
-        <v>1.941660200784833</v>
+        <v>2.012943022478225</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7597,7 +7597,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.209520329962489</v>
+        <v>2.179661947125158</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7605,22 +7605,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08816141980025385</v>
+        <v>0.08829950514367302</v>
       </c>
       <c r="C76">
-        <v>21.40759312345068</v>
+        <v>13.69980769952349</v>
       </c>
       <c r="D76">
-        <v>461.5995931234506</v>
+        <v>460.0998076995235</v>
       </c>
       <c r="E76">
-        <v>39.39199999999994</v>
+        <v>45.59999999999997</v>
       </c>
       <c r="F76">
-        <v>459.3919999999999</v>
+        <v>465.6</v>
       </c>
       <c r="G76">
         <v>19.2</v>
@@ -7641,28 +7641,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M76">
-        <v>34.82191359999999</v>
+        <v>35.29248</v>
       </c>
       <c r="N76">
-        <v>41.07808640000001</v>
+        <v>40.60752000000001</v>
       </c>
       <c r="O76">
-        <v>6.161712960000002</v>
+        <v>6.091128000000001</v>
       </c>
       <c r="P76">
-        <v>34.91637344000001</v>
+        <v>34.51639200000001</v>
       </c>
       <c r="Q76">
-        <v>52.51637344000001</v>
+        <v>52.11639200000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1557046915394379</v>
+        <v>0.159908020574692</v>
       </c>
       <c r="T76">
-        <v>2.012943022478225</v>
+        <v>2.089928469907089</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7679,7 +7679,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.179661947125158</v>
+        <v>2.150599787830155</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7687,22 +7687,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08829950514367302</v>
+        <v>0.08843759048709215</v>
       </c>
       <c r="C77">
-        <v>13.69980769952349</v>
+        <v>6.00173663247989</v>
       </c>
       <c r="D77">
-        <v>460.0998076995235</v>
+        <v>458.6097366324799</v>
       </c>
       <c r="E77">
-        <v>45.59999999999997</v>
+        <v>51.80799999999999</v>
       </c>
       <c r="F77">
-        <v>465.6</v>
+        <v>471.808</v>
       </c>
       <c r="G77">
         <v>19.2</v>
@@ -7723,28 +7723,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M77">
-        <v>35.29248</v>
+        <v>35.7630464</v>
       </c>
       <c r="N77">
-        <v>40.60752000000001</v>
+        <v>40.13695360000001</v>
       </c>
       <c r="O77">
-        <v>6.091128000000001</v>
+        <v>6.020543040000001</v>
       </c>
       <c r="P77">
-        <v>34.51639200000001</v>
+        <v>34.11641056000001</v>
       </c>
       <c r="Q77">
-        <v>52.11639200000001</v>
+        <v>51.71641056000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.159908020574692</v>
+        <v>0.1644616270295506</v>
       </c>
       <c r="T77">
-        <v>2.089928469907089</v>
+        <v>2.173329371288358</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7761,7 +7761,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.150599787830155</v>
+        <v>2.122302422200812</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7769,22 +7769,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08843759048709215</v>
+        <v>0.08857567583051129</v>
       </c>
       <c r="C78">
-        <v>6.00173663247989</v>
+        <v>-1.686714155233517</v>
       </c>
       <c r="D78">
-        <v>458.6097366324799</v>
+        <v>457.1292858447665</v>
       </c>
       <c r="E78">
-        <v>51.80799999999999</v>
+        <v>58.01599999999996</v>
       </c>
       <c r="F78">
-        <v>471.808</v>
+        <v>478.016</v>
       </c>
       <c r="G78">
         <v>19.2</v>
@@ -7805,28 +7805,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M78">
-        <v>35.7630464</v>
+        <v>36.2336128</v>
       </c>
       <c r="N78">
-        <v>40.13695360000001</v>
+        <v>39.6663872</v>
       </c>
       <c r="O78">
-        <v>6.020543040000001</v>
+        <v>5.94995808</v>
       </c>
       <c r="P78">
-        <v>34.11641056000001</v>
+        <v>33.71642912</v>
       </c>
       <c r="Q78">
-        <v>51.71641056000001</v>
+        <v>51.31642912</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1644616270295506</v>
+        <v>0.1694111992630926</v>
       </c>
       <c r="T78">
-        <v>2.173329371288358</v>
+        <v>2.26398252496365</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.122302422200812</v>
+        <v>2.09474005308132</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7851,22 +7851,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08857567583051129</v>
+        <v>0.08871376117393044</v>
       </c>
       <c r="C79">
-        <v>-1.686714155233517</v>
+        <v>-9.365637530301626</v>
       </c>
       <c r="D79">
-        <v>457.1292858447665</v>
+        <v>455.6583624696984</v>
       </c>
       <c r="E79">
-        <v>58.01599999999996</v>
+        <v>64.22399999999999</v>
       </c>
       <c r="F79">
-        <v>478.016</v>
+        <v>484.224</v>
       </c>
       <c r="G79">
         <v>19.2</v>
@@ -7887,28 +7887,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M79">
-        <v>36.2336128</v>
+        <v>36.70417920000001</v>
       </c>
       <c r="N79">
-        <v>39.6663872</v>
+        <v>39.1958208</v>
       </c>
       <c r="O79">
-        <v>5.94995808</v>
+        <v>5.879373119999999</v>
       </c>
       <c r="P79">
-        <v>33.71642912</v>
+        <v>33.31644768</v>
       </c>
       <c r="Q79">
-        <v>51.31642912</v>
+        <v>50.91644768</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1694111992630926</v>
+        <v>0.1748107326087747</v>
       </c>
       <c r="T79">
-        <v>2.26398252496365</v>
+        <v>2.362876874427605</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.09474005308132</v>
+        <v>2.067884411375149</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7933,22 +7933,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08871376117393044</v>
+        <v>0.08885184651734959</v>
       </c>
       <c r="C80">
-        <v>-9.365637530301626</v>
+        <v>-17.03512516795922</v>
       </c>
       <c r="D80">
-        <v>455.6583624696984</v>
+        <v>454.1968748320407</v>
       </c>
       <c r="E80">
-        <v>64.22399999999999</v>
+        <v>70.43199999999996</v>
       </c>
       <c r="F80">
-        <v>484.224</v>
+        <v>490.432</v>
       </c>
       <c r="G80">
         <v>19.2</v>
@@ -7969,28 +7969,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M80">
-        <v>36.70417920000001</v>
+        <v>37.1747456</v>
       </c>
       <c r="N80">
-        <v>39.1958208</v>
+        <v>38.7252544</v>
       </c>
       <c r="O80">
-        <v>5.879373119999999</v>
+        <v>5.808788160000001</v>
       </c>
       <c r="P80">
-        <v>33.31644768</v>
+        <v>32.91646624000001</v>
       </c>
       <c r="Q80">
-        <v>50.91644768</v>
+        <v>50.51646624000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1748107326087747</v>
+        <v>0.1807245072254742</v>
       </c>
       <c r="T80">
-        <v>2.362876874427605</v>
+        <v>2.471189733364318</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -8007,7 +8007,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.067884411375149</v>
+        <v>2.041708659332426</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8015,22 +8015,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08885184651734959</v>
+        <v>0.08898993186076873</v>
       </c>
       <c r="C81">
-        <v>-17.03512516795922</v>
+        <v>-24.69526757103745</v>
       </c>
       <c r="D81">
-        <v>454.1968748320407</v>
+        <v>452.7447324289625</v>
       </c>
       <c r="E81">
-        <v>70.43199999999996</v>
+        <v>76.63999999999999</v>
       </c>
       <c r="F81">
-        <v>490.432</v>
+        <v>496.64</v>
       </c>
       <c r="G81">
         <v>19.2</v>
@@ -8051,28 +8051,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M81">
-        <v>37.1747456</v>
+        <v>37.645312</v>
       </c>
       <c r="N81">
-        <v>38.7252544</v>
+        <v>38.254688</v>
       </c>
       <c r="O81">
-        <v>5.808788160000001</v>
+        <v>5.7382032</v>
       </c>
       <c r="P81">
-        <v>32.91646624000001</v>
+        <v>32.5164848</v>
       </c>
       <c r="Q81">
-        <v>50.51646624000001</v>
+        <v>50.1164848</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1807245072254742</v>
+        <v>0.1872296593038436</v>
       </c>
       <c r="T81">
-        <v>2.471189733364318</v>
+        <v>2.590333878194702</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -8089,7 +8089,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.041708659332426</v>
+        <v>2.01618730109077</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8097,22 +8097,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08898993186076873</v>
+        <v>0.09890471720418788</v>
       </c>
       <c r="C82">
-        <v>-24.69526757103745</v>
+        <v>-115.4318570019385</v>
       </c>
       <c r="D82">
-        <v>452.7447324289625</v>
+        <v>368.2161429980616</v>
       </c>
       <c r="E82">
-        <v>76.63999999999999</v>
+        <v>82.84800000000001</v>
       </c>
       <c r="F82">
-        <v>496.64</v>
+        <v>502.848</v>
       </c>
       <c r="G82">
         <v>19.2</v>
@@ -8133,45 +8133,45 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M82">
-        <v>37.645312</v>
+        <v>45.25632</v>
       </c>
       <c r="N82">
-        <v>38.254688</v>
+        <v>30.64368</v>
       </c>
       <c r="O82">
-        <v>5.7382032</v>
+        <v>4.596552</v>
       </c>
       <c r="P82">
-        <v>32.5164848</v>
+        <v>26.047128</v>
       </c>
       <c r="Q82">
-        <v>50.1164848</v>
+        <v>43.64712800000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1872296593038436</v>
+        <v>0.1944195642325678</v>
       </c>
       <c r="T82">
-        <v>2.590333878194702</v>
+        <v>2.7220195119546</v>
       </c>
       <c r="U82">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V82">
         <v>0.15</v>
       </c>
       <c r="W82">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y82">
-        <v>2.01618730109077</v>
+        <v>1.677113826311994</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8179,22 +8179,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09890471720418788</v>
+        <v>0.09916350254760702</v>
       </c>
       <c r="C83">
-        <v>-115.4318570019385</v>
+        <v>-123.4255145481839</v>
       </c>
       <c r="D83">
-        <v>368.2161429980616</v>
+        <v>366.4304854518161</v>
       </c>
       <c r="E83">
-        <v>82.84800000000001</v>
+        <v>89.05599999999998</v>
       </c>
       <c r="F83">
-        <v>502.848</v>
+        <v>509.056</v>
       </c>
       <c r="G83">
         <v>19.2</v>
@@ -8215,28 +8215,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M83">
-        <v>45.25632</v>
+        <v>45.81504</v>
       </c>
       <c r="N83">
-        <v>30.64368</v>
+        <v>30.08496000000001</v>
       </c>
       <c r="O83">
-        <v>4.596552</v>
+        <v>4.512744000000001</v>
       </c>
       <c r="P83">
-        <v>26.047128</v>
+        <v>25.57221600000001</v>
       </c>
       <c r="Q83">
-        <v>43.64712800000001</v>
+        <v>43.17221600000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1944195642325678</v>
+        <v>0.2024083474867057</v>
       </c>
       <c r="T83">
-        <v>2.7220195119546</v>
+        <v>2.868336882798932</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.677113826311994</v>
+        <v>1.656661218674043</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8261,22 +8261,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09916350254760702</v>
+        <v>0.09942228789102617</v>
       </c>
       <c r="C84">
-        <v>-123.4255145481839</v>
+        <v>-131.4019366492626</v>
       </c>
       <c r="D84">
-        <v>366.4304854518161</v>
+        <v>364.6620633507374</v>
       </c>
       <c r="E84">
-        <v>89.05599999999998</v>
+        <v>95.26400000000001</v>
       </c>
       <c r="F84">
-        <v>509.056</v>
+        <v>515.264</v>
       </c>
       <c r="G84">
         <v>19.2</v>
@@ -8297,28 +8297,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M84">
-        <v>45.81504</v>
+        <v>46.37376</v>
       </c>
       <c r="N84">
-        <v>30.08496000000001</v>
+        <v>29.52624000000001</v>
       </c>
       <c r="O84">
-        <v>4.512744000000001</v>
+        <v>4.428936000000001</v>
       </c>
       <c r="P84">
-        <v>25.57221600000001</v>
+        <v>25.09730400000001</v>
       </c>
       <c r="Q84">
-        <v>43.17221600000001</v>
+        <v>42.69730400000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2024083474867057</v>
+        <v>0.2113369875942716</v>
       </c>
       <c r="T84">
-        <v>2.868336882798932</v>
+        <v>3.031868061977891</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.656661218674043</v>
+        <v>1.636701444955078</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8343,22 +8343,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09942228789102617</v>
+        <v>0.09968107323444531</v>
       </c>
       <c r="C85">
-        <v>-131.4019366492626</v>
+        <v>-139.3613716454724</v>
       </c>
       <c r="D85">
-        <v>364.6620633507374</v>
+        <v>362.9106283545276</v>
       </c>
       <c r="E85">
-        <v>95.26400000000001</v>
+        <v>101.472</v>
       </c>
       <c r="F85">
-        <v>515.264</v>
+        <v>521.472</v>
       </c>
       <c r="G85">
         <v>19.2</v>
@@ -8379,28 +8379,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M85">
-        <v>46.37376</v>
+        <v>46.93248</v>
       </c>
       <c r="N85">
-        <v>29.52624000000001</v>
+        <v>28.96752000000001</v>
       </c>
       <c r="O85">
-        <v>4.428936000000001</v>
+        <v>4.345128000000001</v>
       </c>
       <c r="P85">
-        <v>25.09730400000001</v>
+        <v>24.622392</v>
       </c>
       <c r="Q85">
-        <v>42.69730400000001</v>
+        <v>42.22239200000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2113369875942716</v>
+        <v>0.2213817077152832</v>
       </c>
       <c r="T85">
-        <v>3.031868061977891</v>
+        <v>3.215840638554219</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8417,7 +8417,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.636701444955078</v>
+        <v>1.617216903943708</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8425,22 +8425,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09968107323444531</v>
+        <v>0.09993985857786446</v>
       </c>
       <c r="C86">
-        <v>-139.3613716454724</v>
+        <v>-147.3040631289035</v>
       </c>
       <c r="D86">
-        <v>362.9106283545276</v>
+        <v>361.1759368710964</v>
       </c>
       <c r="E86">
-        <v>101.472</v>
+        <v>107.6799999999999</v>
       </c>
       <c r="F86">
-        <v>521.472</v>
+        <v>527.6799999999999</v>
       </c>
       <c r="G86">
         <v>19.2</v>
@@ -8461,28 +8461,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M86">
-        <v>46.93248</v>
+        <v>47.49119999999999</v>
       </c>
       <c r="N86">
-        <v>28.96752000000001</v>
+        <v>28.40880000000001</v>
       </c>
       <c r="O86">
-        <v>4.345128000000001</v>
+        <v>4.261320000000002</v>
       </c>
       <c r="P86">
-        <v>24.622392</v>
+        <v>24.14748000000001</v>
       </c>
       <c r="Q86">
-        <v>42.22239200000001</v>
+        <v>41.74748000000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2213817077152831</v>
+        <v>0.2327657238524297</v>
       </c>
       <c r="T86">
-        <v>3.215840638554217</v>
+        <v>3.42434289200739</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.617216903943708</v>
+        <v>1.598190822720841</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8507,22 +8507,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09993985857786446</v>
+        <v>0.1001986439212836</v>
       </c>
       <c r="C87">
-        <v>-147.3040631289035</v>
+        <v>-155.2302500563784</v>
       </c>
       <c r="D87">
-        <v>361.1759368710964</v>
+        <v>359.4577499436215</v>
       </c>
       <c r="E87">
-        <v>107.6799999999999</v>
+        <v>113.8879999999999</v>
       </c>
       <c r="F87">
-        <v>527.6799999999999</v>
+        <v>533.8879999999999</v>
       </c>
       <c r="G87">
         <v>19.2</v>
@@ -8543,28 +8543,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M87">
-        <v>47.49119999999999</v>
+        <v>48.04991999999999</v>
       </c>
       <c r="N87">
-        <v>28.40880000000001</v>
+        <v>27.85008000000001</v>
       </c>
       <c r="O87">
-        <v>4.261320000000002</v>
+        <v>4.177512000000002</v>
       </c>
       <c r="P87">
-        <v>24.14748000000001</v>
+        <v>23.67256800000001</v>
       </c>
       <c r="Q87">
-        <v>41.74748000000001</v>
+        <v>41.27256800000001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2327657238524297</v>
+        <v>0.2457760280091685</v>
       </c>
       <c r="T87">
-        <v>3.42434289200739</v>
+        <v>3.662631181668157</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8581,7 +8581,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.598190822720841</v>
+        <v>1.579607208503157</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8589,22 +8589,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1001986439212836</v>
+        <v>0.1004574292647027</v>
       </c>
       <c r="C88">
-        <v>-155.2302500563784</v>
+        <v>-163.1401668591855</v>
       </c>
       <c r="D88">
-        <v>359.4577499436215</v>
+        <v>357.7558331408145</v>
       </c>
       <c r="E88">
-        <v>113.8879999999999</v>
+        <v>120.096</v>
       </c>
       <c r="F88">
-        <v>533.8879999999999</v>
+        <v>540.096</v>
       </c>
       <c r="G88">
         <v>19.2</v>
@@ -8625,28 +8625,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M88">
-        <v>48.04991999999999</v>
+        <v>48.60864</v>
       </c>
       <c r="N88">
-        <v>27.85008000000001</v>
+        <v>27.29136</v>
       </c>
       <c r="O88">
-        <v>4.177512000000002</v>
+        <v>4.093704000000001</v>
       </c>
       <c r="P88">
-        <v>23.67256800000001</v>
+        <v>23.197656</v>
       </c>
       <c r="Q88">
-        <v>41.27256800000001</v>
+        <v>40.797656</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2457760280091685</v>
+        <v>0.2607879174207902</v>
       </c>
       <c r="T88">
-        <v>3.662631181668157</v>
+        <v>3.937579208199812</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8663,7 +8663,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.579607208503157</v>
+        <v>1.561450803807718</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8671,22 +8671,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1004574292647027</v>
+        <v>0.1007162146081219</v>
       </c>
       <c r="C89">
-        <v>-163.1401668591855</v>
+        <v>-171.0340435497077</v>
       </c>
       <c r="D89">
-        <v>357.7558331408145</v>
+        <v>356.0699564502923</v>
       </c>
       <c r="E89">
-        <v>120.096</v>
+        <v>126.304</v>
       </c>
       <c r="F89">
-        <v>540.096</v>
+        <v>546.304</v>
       </c>
       <c r="G89">
         <v>19.2</v>
@@ -8707,28 +8707,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M89">
-        <v>48.60864</v>
+        <v>49.16736</v>
       </c>
       <c r="N89">
-        <v>27.29136</v>
+        <v>26.73264000000001</v>
       </c>
       <c r="O89">
-        <v>4.093704000000001</v>
+        <v>4.009896000000001</v>
       </c>
       <c r="P89">
-        <v>23.197656</v>
+        <v>22.72274400000001</v>
       </c>
       <c r="Q89">
-        <v>40.797656</v>
+        <v>40.32274400000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2607879174207902</v>
+        <v>0.2783017884010157</v>
       </c>
       <c r="T89">
-        <v>3.937579208199812</v>
+        <v>4.258351905820078</v>
       </c>
       <c r="U89">
         <v>0.09</v>
@@ -8745,7 +8745,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.561450803807718</v>
+        <v>1.54370704467354</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8753,22 +8753,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1007162146081219</v>
+        <v>0.100974999951541</v>
       </c>
       <c r="C90">
-        <v>-171.0340435497077</v>
+        <v>-178.9121058250526</v>
       </c>
       <c r="D90">
-        <v>356.0699564502923</v>
+        <v>354.3998941749473</v>
       </c>
       <c r="E90">
-        <v>126.304</v>
+        <v>132.5119999999999</v>
       </c>
       <c r="F90">
-        <v>546.304</v>
+        <v>552.5119999999999</v>
       </c>
       <c r="G90">
         <v>19.2</v>
@@ -8789,28 +8789,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M90">
-        <v>49.16736</v>
+        <v>49.72608</v>
       </c>
       <c r="N90">
-        <v>26.73264000000001</v>
+        <v>26.17392000000001</v>
       </c>
       <c r="O90">
-        <v>4.009896000000001</v>
+        <v>3.926088000000001</v>
       </c>
       <c r="P90">
-        <v>22.72274400000001</v>
+        <v>22.24783200000001</v>
       </c>
       <c r="Q90">
-        <v>40.32274400000001</v>
+        <v>39.84783200000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2783017884010157</v>
+        <v>0.2989999995594639</v>
       </c>
       <c r="T90">
-        <v>4.258351905820078</v>
+        <v>4.637446912098572</v>
       </c>
       <c r="U90">
         <v>0.09</v>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.54370704467354</v>
+        <v>1.52636202169968</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8835,22 +8835,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.100974999951541</v>
+        <v>0.1012337852949602</v>
       </c>
       <c r="C91">
-        <v>-178.9121058250526</v>
+        <v>-186.7745751677788</v>
       </c>
       <c r="D91">
-        <v>354.3998941749473</v>
+        <v>352.7454248322213</v>
       </c>
       <c r="E91">
-        <v>132.5119999999999</v>
+        <v>138.72</v>
       </c>
       <c r="F91">
-        <v>552.5119999999999</v>
+        <v>558.72</v>
       </c>
       <c r="G91">
         <v>19.2</v>
@@ -8871,28 +8871,28 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M91">
-        <v>49.72608</v>
+        <v>50.2848</v>
       </c>
       <c r="N91">
-        <v>26.17392000000001</v>
+        <v>25.61520000000001</v>
       </c>
       <c r="O91">
-        <v>3.926088000000001</v>
+        <v>3.842280000000001</v>
       </c>
       <c r="P91">
-        <v>22.24783200000001</v>
+        <v>21.77292000000001</v>
       </c>
       <c r="Q91">
-        <v>39.84783200000001</v>
+        <v>39.37292000000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2989999995594639</v>
+        <v>0.3238378529496018</v>
       </c>
       <c r="T91">
-        <v>4.637446912098572</v>
+        <v>5.092360919632767</v>
       </c>
       <c r="U91">
         <v>0.09</v>
@@ -8909,7 +8909,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.52636202169968</v>
+        <v>1.509402443680794</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8917,22 +8917,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1012337852949602</v>
+        <v>0.1474983327090399</v>
       </c>
       <c r="C92">
-        <v>-186.7745751677788</v>
+        <v>-353.4533223032366</v>
       </c>
       <c r="D92">
-        <v>352.7454248322213</v>
+        <v>192.2746776967634</v>
       </c>
       <c r="E92">
-        <v>138.72</v>
+        <v>144.928</v>
       </c>
       <c r="F92">
-        <v>558.72</v>
+        <v>564.928</v>
       </c>
       <c r="G92">
         <v>19.2</v>
@@ -8953,45 +8953,45 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M92">
-        <v>50.2848</v>
+        <v>82.93143040000001</v>
       </c>
       <c r="N92">
-        <v>25.61520000000001</v>
+        <v>-7.031430400000005</v>
       </c>
       <c r="O92">
-        <v>3.842280000000001</v>
+        <v>-1.054714560000001</v>
       </c>
       <c r="P92">
-        <v>21.77292000000001</v>
+        <v>-5.976715840000004</v>
       </c>
       <c r="Q92">
-        <v>39.37292000000001</v>
+        <v>11.62328416</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3238378529496018</v>
+        <v>0.3583285822195724</v>
       </c>
       <c r="T92">
-        <v>5.092360919632767</v>
+        <v>5.724070738856086</v>
       </c>
       <c r="U92">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.15</v>
+        <v>0.1372820888906313</v>
       </c>
       <c r="W92">
-        <v>0.0765</v>
+        <v>0.1266469893508554</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y92">
-        <v>1.509402443680794</v>
+        <v>0.9152139259375417</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8999,22 +8999,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1474983327090399</v>
+        <v>0.1485083327090399</v>
       </c>
       <c r="C93">
-        <v>-353.4533223032366</v>
+        <v>-361.552088313662</v>
       </c>
       <c r="D93">
-        <v>192.2746776967634</v>
+        <v>190.383911686338</v>
       </c>
       <c r="E93">
-        <v>144.928</v>
+        <v>151.136</v>
       </c>
       <c r="F93">
-        <v>564.928</v>
+        <v>571.136</v>
       </c>
       <c r="G93">
         <v>19.2</v>
@@ -9035,37 +9035,37 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M93">
-        <v>82.93143040000001</v>
+        <v>83.8427648</v>
       </c>
       <c r="N93">
-        <v>-7.031430400000005</v>
+        <v>-7.942764799999992</v>
       </c>
       <c r="O93">
-        <v>-1.054714560000001</v>
+        <v>-1.191414719999999</v>
       </c>
       <c r="P93">
-        <v>-5.976715840000004</v>
+        <v>-6.751350079999993</v>
       </c>
       <c r="Q93">
-        <v>11.62328416</v>
+        <v>10.84864992000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3583285822195724</v>
+        <v>0.397394654997019</v>
       </c>
       <c r="T93">
-        <v>5.724070738856086</v>
+        <v>6.439579581213097</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.1372820888906313</v>
+        <v>0.1357898922722549</v>
       </c>
       <c r="W93">
-        <v>0.1266469893508554</v>
+        <v>0.126866043814433</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.9152139259375417</v>
+        <v>0.9052659484816991</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9081,22 +9081,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1485083327090399</v>
+        <v>0.1495183327090399</v>
       </c>
       <c r="C94">
-        <v>-361.552088313662</v>
+        <v>-369.6140300979233</v>
       </c>
       <c r="D94">
-        <v>190.383911686338</v>
+        <v>188.5299699020767</v>
       </c>
       <c r="E94">
-        <v>151.136</v>
+        <v>157.3439999999999</v>
       </c>
       <c r="F94">
-        <v>571.136</v>
+        <v>577.3439999999999</v>
       </c>
       <c r="G94">
         <v>19.2</v>
@@ -9117,37 +9117,37 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M94">
-        <v>83.8427648</v>
+        <v>84.7540992</v>
       </c>
       <c r="N94">
-        <v>-7.942764799999992</v>
+        <v>-8.854099199999993</v>
       </c>
       <c r="O94">
-        <v>-1.191414719999999</v>
+        <v>-1.328114879999999</v>
       </c>
       <c r="P94">
-        <v>-6.751350079999993</v>
+        <v>-7.525984319999994</v>
       </c>
       <c r="Q94">
-        <v>10.84864992000001</v>
+        <v>10.07401568000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.397394654997019</v>
+        <v>0.4476224628537361</v>
       </c>
       <c r="T94">
-        <v>6.439579581213097</v>
+        <v>7.359519521386399</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.1357898922722549</v>
+        <v>0.134329785903736</v>
       </c>
       <c r="W94">
-        <v>0.126866043814433</v>
+        <v>0.1270803874293316</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9155,7 +9155,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.9052659484816991</v>
+        <v>0.8955319060249065</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9163,22 +9163,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1495183327090399</v>
+        <v>0.1505283327090399</v>
       </c>
       <c r="C95">
-        <v>-369.6140300979233</v>
+        <v>-377.6402130544889</v>
       </c>
       <c r="D95">
-        <v>188.5299699020767</v>
+        <v>186.7117869455112</v>
       </c>
       <c r="E95">
-        <v>157.3439999999999</v>
+        <v>163.552</v>
       </c>
       <c r="F95">
-        <v>577.3439999999999</v>
+        <v>583.552</v>
       </c>
       <c r="G95">
         <v>19.2</v>
@@ -9199,37 +9199,37 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M95">
-        <v>84.7540992</v>
+        <v>85.66543360000001</v>
       </c>
       <c r="N95">
-        <v>-8.854099199999993</v>
+        <v>-9.765433600000009</v>
       </c>
       <c r="O95">
-        <v>-1.328114879999999</v>
+        <v>-1.464815040000001</v>
       </c>
       <c r="P95">
-        <v>-7.525984319999994</v>
+        <v>-8.300618560000007</v>
       </c>
       <c r="Q95">
-        <v>10.07401568000001</v>
+        <v>9.299381439999994</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4476224628537361</v>
+        <v>0.5145928733293589</v>
       </c>
       <c r="T95">
-        <v>7.359519521386399</v>
+        <v>8.586106108284133</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.134329785903736</v>
+        <v>0.1329007456281643</v>
       </c>
       <c r="W95">
-        <v>0.1270803874293316</v>
+        <v>0.1272901705417855</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8955319060249065</v>
+        <v>0.8860049708544286</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9245,22 +9245,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1505283327090399</v>
+        <v>0.1515383327090399</v>
       </c>
       <c r="C96">
-        <v>-377.6402130544889</v>
+        <v>-385.6316618755884</v>
       </c>
       <c r="D96">
-        <v>186.7117869455112</v>
+        <v>184.9283381244116</v>
       </c>
       <c r="E96">
-        <v>163.552</v>
+        <v>169.76</v>
       </c>
       <c r="F96">
-        <v>583.552</v>
+        <v>589.76</v>
       </c>
       <c r="G96">
         <v>19.2</v>
@@ -9281,37 +9281,37 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M96">
-        <v>85.66543360000001</v>
+        <v>86.576768</v>
       </c>
       <c r="N96">
-        <v>-9.765433600000009</v>
+        <v>-10.676768</v>
       </c>
       <c r="O96">
-        <v>-1.464815040000001</v>
+        <v>-1.601515199999999</v>
       </c>
       <c r="P96">
-        <v>-8.300618560000007</v>
+        <v>-9.075252799999996</v>
       </c>
       <c r="Q96">
-        <v>9.299381439999994</v>
+        <v>8.524747200000006</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5145928733293589</v>
+        <v>0.608351447995231</v>
       </c>
       <c r="T96">
-        <v>8.586106108284133</v>
+        <v>10.30332732994097</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.1329007456281643</v>
+        <v>0.1315017904110257</v>
       </c>
       <c r="W96">
-        <v>0.1272901705417855</v>
+        <v>0.1274955371676614</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8860049708544286</v>
+        <v>0.8766786027401716</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9327,22 +9327,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1515383327090399</v>
+        <v>0.1525483327090399</v>
       </c>
       <c r="C97">
-        <v>-385.6316618755884</v>
+        <v>-393.5893624729246</v>
       </c>
       <c r="D97">
-        <v>184.9283381244116</v>
+        <v>183.1786375270754</v>
       </c>
       <c r="E97">
-        <v>169.76</v>
+        <v>175.968</v>
       </c>
       <c r="F97">
-        <v>589.76</v>
+        <v>595.968</v>
       </c>
       <c r="G97">
         <v>19.2</v>
@@ -9363,37 +9363,37 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M97">
-        <v>86.576768</v>
+        <v>87.4881024</v>
       </c>
       <c r="N97">
-        <v>-10.676768</v>
+        <v>-11.5881024</v>
       </c>
       <c r="O97">
-        <v>-1.601515199999999</v>
+        <v>-1.738215359999999</v>
       </c>
       <c r="P97">
-        <v>-9.075252799999996</v>
+        <v>-9.849887039999997</v>
       </c>
       <c r="Q97">
-        <v>8.524747200000006</v>
+        <v>7.750112960000004</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.608351447995231</v>
+        <v>0.7489893099940391</v>
       </c>
       <c r="T97">
-        <v>10.30332732994097</v>
+        <v>12.87915916242621</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.1315017904110257</v>
+        <v>0.1301319800942442</v>
       </c>
       <c r="W97">
-        <v>0.1274955371676614</v>
+        <v>0.127696625322165</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8766786027401716</v>
+        <v>0.8675465339616282</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9409,22 +9409,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1525483327090399</v>
+        <v>0.1535583327090399</v>
       </c>
       <c r="C98">
-        <v>-393.5893624729246</v>
+        <v>-401.5142637950887</v>
       </c>
       <c r="D98">
-        <v>183.1786375270754</v>
+        <v>181.4617362049113</v>
       </c>
       <c r="E98">
-        <v>175.968</v>
+        <v>182.1759999999999</v>
       </c>
       <c r="F98">
-        <v>595.968</v>
+        <v>602.1759999999999</v>
       </c>
       <c r="G98">
         <v>19.2</v>
@@ -9445,37 +9445,37 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M98">
-        <v>87.4881024</v>
+        <v>88.3994368</v>
       </c>
       <c r="N98">
-        <v>-11.5881024</v>
+        <v>-12.4994368</v>
       </c>
       <c r="O98">
-        <v>-1.738215359999999</v>
+        <v>-1.87491552</v>
       </c>
       <c r="P98">
-        <v>-9.849887039999997</v>
+        <v>-10.62452128</v>
       </c>
       <c r="Q98">
-        <v>7.750112960000004</v>
+        <v>6.975478720000003</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7489893099940371</v>
+        <v>0.9833857466587164</v>
       </c>
       <c r="T98">
-        <v>12.87915916242618</v>
+        <v>17.17221221656824</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.1301319800942442</v>
+        <v>0.1287904132891489</v>
       </c>
       <c r="W98">
-        <v>0.127696625322165</v>
+        <v>0.127893567329153</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8675465339616282</v>
+        <v>0.8586027552609928</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9491,22 +9491,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1535583327090399</v>
+        <v>0.1545683327090399</v>
       </c>
       <c r="C99">
-        <v>-401.5142637950887</v>
+        <v>-409.4072795437186</v>
       </c>
       <c r="D99">
-        <v>181.4617362049113</v>
+        <v>179.7767204562813</v>
       </c>
       <c r="E99">
-        <v>182.1759999999999</v>
+        <v>188.3839999999999</v>
       </c>
       <c r="F99">
-        <v>602.1759999999999</v>
+        <v>608.3839999999999</v>
       </c>
       <c r="G99">
         <v>19.2</v>
@@ -9527,37 +9527,37 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M99">
-        <v>88.3994368</v>
+        <v>89.31077119999999</v>
       </c>
       <c r="N99">
-        <v>-12.4994368</v>
+        <v>-13.41077119999999</v>
       </c>
       <c r="O99">
-        <v>-1.87491552</v>
+        <v>-2.011615679999998</v>
       </c>
       <c r="P99">
-        <v>-10.62452128</v>
+        <v>-11.39915551999999</v>
       </c>
       <c r="Q99">
-        <v>6.975478720000003</v>
+        <v>6.200844480000015</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9833857466587164</v>
+        <v>1.452178619988074</v>
       </c>
       <c r="T99">
-        <v>17.17221221656824</v>
+        <v>25.75831832485236</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.1287904132891489</v>
+        <v>0.1274762253984433</v>
       </c>
       <c r="W99">
-        <v>0.127893567329153</v>
+        <v>0.1280864901115085</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8586027552609928</v>
+        <v>0.8498415026562889</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9573,22 +9573,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1545683327090399</v>
+        <v>0.1555783327090399</v>
       </c>
       <c r="C100">
-        <v>-409.4072795437186</v>
+        <v>-417.2692897949228</v>
       </c>
       <c r="D100">
-        <v>179.7767204562813</v>
+        <v>178.1227102050773</v>
       </c>
       <c r="E100">
-        <v>188.3839999999999</v>
+        <v>194.592</v>
       </c>
       <c r="F100">
-        <v>608.3839999999999</v>
+        <v>614.592</v>
       </c>
       <c r="G100">
         <v>19.2</v>
@@ -9609,37 +9609,37 @@
         <v>75.90000000000001</v>
       </c>
       <c r="M100">
-        <v>89.31077119999999</v>
+        <v>90.22210560000001</v>
       </c>
       <c r="N100">
-        <v>-13.41077119999999</v>
+        <v>-14.3221056</v>
       </c>
       <c r="O100">
-        <v>-2.011615679999998</v>
+        <v>-2.14831584</v>
       </c>
       <c r="P100">
-        <v>-11.39915551999999</v>
+        <v>-12.17378976</v>
       </c>
       <c r="Q100">
-        <v>6.200844480000015</v>
+        <v>5.426210240000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.452178619988074</v>
+        <v>2.858557239976149</v>
       </c>
       <c r="T100">
-        <v>25.75831832485236</v>
+        <v>51.51663664970472</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.1274762253984433</v>
+        <v>0.126188586758055</v>
       </c>
       <c r="W100">
-        <v>0.1280864901115085</v>
+        <v>0.1282755154639175</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9647,91 +9647,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8498415026562889</v>
+        <v>0.8412572450537</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1555783327090399</v>
-      </c>
-      <c r="C101">
-        <v>-417.2692897949228</v>
-      </c>
-      <c r="D101">
-        <v>178.1227102050773</v>
-      </c>
-      <c r="E101">
-        <v>194.592</v>
-      </c>
-      <c r="F101">
-        <v>614.592</v>
-      </c>
-      <c r="G101">
-        <v>19.2</v>
-      </c>
-      <c r="H101">
-        <v>200.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>93.5</v>
-      </c>
-      <c r="K101">
-        <v>17.6</v>
-      </c>
-      <c r="L101">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="M101">
-        <v>90.22210560000001</v>
-      </c>
-      <c r="N101">
-        <v>-14.3221056</v>
-      </c>
-      <c r="O101">
-        <v>-2.14831584</v>
-      </c>
-      <c r="P101">
-        <v>-12.17378976</v>
-      </c>
-      <c r="Q101">
-        <v>5.426210240000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.858557239976149</v>
-      </c>
-      <c r="T101">
-        <v>51.51663664970472</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.126188586758055</v>
-      </c>
-      <c r="W101">
-        <v>0.1282755154639175</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8412572450537</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
